--- a/Dataset_S1.xlsx
+++ b/Dataset_S1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inmav/Desktop/Inma/IDIBAPS/CoA_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C68A9B-50A6-9C44-AB68-E5AECAB8332F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB334336-3FFE-EB48-AAB5-5CB25B875A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="7" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
   <si>
     <t>GA</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>Maternal age</t>
-  </si>
-  <si>
-    <t>Maternal date of birth</t>
   </si>
   <si>
     <t>ln_predicted_ist</t>
@@ -254,16 +251,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -589,7 +584,7 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -601,81 +596,81 @@
         <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="W1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2">
         <v>30.57</v>
@@ -686,10 +681,10 @@
       <c r="D2">
         <v>30.71</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="8">
         <v>63</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="8">
         <v>1.68</v>
       </c>
       <c r="G2">
@@ -702,54 +697,54 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="11">
+        <v>18</v>
+      </c>
+      <c r="K2" s="9">
         <v>4.3899999999999997</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="9">
         <v>4</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="8">
         <v>4.3</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="8">
         <v>4.2</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="9">
         <v>0.98</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="9">
         <v>1.05</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="9">
         <v>0.85</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="10">
         <v>1.1767068300000001</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="10">
         <v>1.3640000000000001</v>
       </c>
-      <c r="T2" s="12">
+      <c r="T2" s="10">
         <v>1.415</v>
       </c>
-      <c r="U2" s="12">
+      <c r="U2" s="10">
         <v>0.57599999999999996</v>
       </c>
-      <c r="V2" s="12">
+      <c r="V2" s="10">
         <v>0.112</v>
       </c>
-      <c r="W2" s="10">
+      <c r="W2" s="8">
         <v>3.8159999999999998</v>
       </c>
-      <c r="X2" s="10">
+      <c r="X2" s="8">
         <v>2.8370000000000002</v>
       </c>
-      <c r="Y2" s="10">
+      <c r="Y2" s="8">
         <v>0.82799999999999996</v>
       </c>
-      <c r="Z2" s="10">
+      <c r="Z2" s="8">
         <v>2.0779999999999998</v>
       </c>
       <c r="AA2" s="1">
@@ -764,7 +759,7 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>30.71</v>
@@ -791,54 +786,54 @@
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="11">
+        <v>18</v>
+      </c>
+      <c r="K3" s="9">
         <v>4.41</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="9">
         <v>4.0199999999999996</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="8">
         <v>4.3</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="8">
         <v>4</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="9">
         <v>0.97</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="9">
         <v>0.99</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="9">
         <v>0.9</v>
       </c>
-      <c r="R3" s="12">
+      <c r="R3" s="10">
         <v>1.10747664</v>
       </c>
-      <c r="S3" s="12">
+      <c r="S3" s="10">
         <v>1.37</v>
       </c>
-      <c r="T3" s="12">
+      <c r="T3" s="10">
         <v>1.4219999999999999</v>
       </c>
-      <c r="U3" s="12">
+      <c r="U3" s="10">
         <v>0.54200000000000004</v>
       </c>
-      <c r="V3" s="12">
+      <c r="V3" s="10">
         <v>-0.20100000000000001</v>
       </c>
-      <c r="W3" s="10">
+      <c r="W3" s="8">
         <v>2.9910000000000001</v>
       </c>
-      <c r="X3" s="10">
+      <c r="X3" s="8">
         <v>2.387</v>
       </c>
-      <c r="Y3" s="10">
+      <c r="Y3" s="8">
         <v>1.012</v>
       </c>
-      <c r="Z3" s="10">
+      <c r="Z3" s="8">
         <v>2.2589999999999999</v>
       </c>
       <c r="AA3" s="1">
@@ -853,7 +848,7 @@
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>30.43</v>
@@ -880,54 +875,54 @@
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="11">
+        <v>19</v>
+      </c>
+      <c r="K4" s="9">
         <v>4.3600000000000003</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="9">
         <v>3.99</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="8">
         <v>4</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="8">
         <v>4.2</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="9">
         <v>0.92</v>
       </c>
-      <c r="P4" s="11">
+      <c r="P4" s="9">
         <v>1.05</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="9">
         <v>0.95</v>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="10">
         <v>1.0562913899999999</v>
       </c>
-      <c r="S4" s="12">
+      <c r="S4" s="10">
         <v>1.3580000000000001</v>
       </c>
-      <c r="T4" s="12">
+      <c r="T4" s="10">
         <v>1.409</v>
       </c>
-      <c r="U4" s="12">
+      <c r="U4" s="10">
         <v>0.17</v>
       </c>
-      <c r="V4" s="12">
+      <c r="V4" s="10">
         <v>0.14899999999999999</v>
       </c>
-      <c r="W4" s="10">
+      <c r="W4" s="8">
         <v>4.46</v>
       </c>
-      <c r="X4" s="10">
+      <c r="X4" s="8">
         <v>4.7220000000000004</v>
       </c>
-      <c r="Y4" s="10">
+      <c r="Y4" s="8">
         <v>0.85299999999999998</v>
       </c>
-      <c r="Z4" s="10">
+      <c r="Z4" s="8">
         <v>1.4590000000000001</v>
       </c>
       <c r="AA4" s="1">
@@ -942,7 +937,7 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>33</v>
@@ -953,10 +948,10 @@
       <c r="D5">
         <v>39.31</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>81</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="8">
         <v>1.59</v>
       </c>
       <c r="G5">
@@ -969,54 +964,54 @@
         <v>6</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="11">
+        <v>18</v>
+      </c>
+      <c r="K5" s="9">
         <v>4.8499999999999996</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="9">
         <v>4.3</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="8">
         <v>4.2</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="9">
         <v>0.87</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="9">
         <v>1.02</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="9">
         <v>0.85</v>
       </c>
-      <c r="R5" s="12">
+      <c r="R5" s="10">
         <v>1.1791666700000001</v>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="10">
         <v>1.458</v>
       </c>
-      <c r="T5" s="12">
+      <c r="T5" s="10">
         <v>1.522</v>
       </c>
-      <c r="U5" s="12">
+      <c r="U5" s="10">
         <v>-0.13800000000000001</v>
       </c>
-      <c r="V5" s="12">
+      <c r="V5" s="10">
         <v>-0.23</v>
       </c>
-      <c r="W5" s="10">
+      <c r="W5" s="8">
         <v>3.714</v>
       </c>
-      <c r="X5" s="10">
+      <c r="X5" s="8">
         <v>2.4220000000000002</v>
       </c>
-      <c r="Y5" s="10">
+      <c r="Y5" s="8">
         <v>1.25</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="Z5" s="8">
         <v>2.266</v>
       </c>
       <c r="AA5" s="1">
@@ -1031,7 +1026,7 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>32.14</v>
@@ -1052,54 +1047,54 @@
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="11">
+        <v>19</v>
+      </c>
+      <c r="K6" s="9">
         <v>4.68</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="9">
         <v>4.2</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="9">
         <v>0.88</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="9">
         <v>1.05</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="9">
         <v>0.93</v>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="10">
         <v>1.0703517600000001</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="10">
         <v>1.425</v>
       </c>
-      <c r="T6" s="12">
+      <c r="T6" s="10">
         <v>1.4850000000000001</v>
       </c>
-      <c r="U6" s="12">
+      <c r="U6" s="10">
         <v>-8.7999999999999995E-2</v>
       </c>
-      <c r="V6" s="12">
+      <c r="V6" s="10">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="W6" s="10">
+      <c r="W6" s="8">
         <v>2.7589999999999999</v>
       </c>
-      <c r="X6" s="10">
+      <c r="X6" s="8">
         <v>1.7949999999999999</v>
       </c>
-      <c r="Y6" s="10">
+      <c r="Y6" s="8">
         <v>0.83199999999999996</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="Z6" s="8">
         <v>1.7509999999999999</v>
       </c>
       <c r="AA6" s="1">
@@ -1114,7 +1109,7 @@
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>37.43</v>
@@ -1135,54 +1130,54 @@
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="11">
+        <v>20</v>
+      </c>
+      <c r="K7" s="9">
         <v>5.68</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="9">
         <v>4.84</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="8">
         <v>4.3</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="8">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="9">
         <v>0.76</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="9">
         <v>1.05</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="9">
         <v>0.9</v>
       </c>
-      <c r="R7" s="12">
+      <c r="R7" s="10">
         <v>1.1059431500000001</v>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="10">
         <v>1.6120000000000001</v>
       </c>
-      <c r="T7" s="12">
+      <c r="T7" s="10">
         <v>1.698</v>
       </c>
-      <c r="U7" s="12">
+      <c r="U7" s="10">
         <v>-0.93500000000000005</v>
       </c>
-      <c r="V7" s="12">
+      <c r="V7" s="10">
         <v>-0.39100000000000001</v>
       </c>
-      <c r="W7" s="10">
+      <c r="W7" s="8">
         <v>4.9649999999999999</v>
       </c>
-      <c r="X7" s="10">
+      <c r="X7" s="8">
         <v>3.0790000000000002</v>
       </c>
-      <c r="Y7" s="10">
+      <c r="Y7" s="8">
         <v>1.012</v>
       </c>
-      <c r="Z7" s="10">
+      <c r="Z7" s="8">
         <v>1.9510000000000001</v>
       </c>
       <c r="AA7" s="1">
@@ -1197,7 +1192,7 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8">
         <v>28.29</v>
@@ -1221,54 +1216,54 @@
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="11">
+        <v>19</v>
+      </c>
+      <c r="K8" s="9">
         <v>3.96</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="9">
         <v>3.72</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="8">
         <v>4</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="8">
         <v>3.7</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="9">
         <v>1.01</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="9">
         <v>1</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="9">
         <v>0.91</v>
       </c>
-      <c r="R8" s="12">
+      <c r="R8" s="10">
         <v>1.09375</v>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="10">
         <v>1.2689999999999999</v>
       </c>
-      <c r="T8" s="12">
+      <c r="T8" s="10">
         <v>1.3069999999999999</v>
       </c>
-      <c r="U8" s="12">
+      <c r="U8" s="10">
         <v>0.71399999999999997</v>
       </c>
-      <c r="V8" s="12">
+      <c r="V8" s="10">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="W8" s="10">
+      <c r="W8" s="8">
         <v>2.7189999999999999</v>
       </c>
-      <c r="X8" s="10">
+      <c r="X8" s="8">
         <v>2.4529999999999998</v>
       </c>
-      <c r="Y8" s="10">
+      <c r="Y8" s="8">
         <v>0.97</v>
       </c>
-      <c r="Z8" s="10">
+      <c r="Z8" s="8">
         <v>1.532</v>
       </c>
       <c r="AA8" s="1">
@@ -1282,22 +1277,22 @@
       <c r="AC8" s="4"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1331,40 +1326,40 @@
         <f t="shared" ref="H10" si="1">AVERAGE(H2:H8)</f>
         <v>3201.8571428571427</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11">
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9">
         <v>4.17</v>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="9">
         <v>4.29</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11">
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9">
         <v>0.9</v>
       </c>
-      <c r="R10" s="11">
+      <c r="R10" s="9">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="11">
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="9">
         <v>0.12</v>
       </c>
-      <c r="V10" s="11">
+      <c r="V10" s="9">
         <v>-0.08</v>
       </c>
-      <c r="W10" s="11">
+      <c r="W10" s="9">
         <v>3.63</v>
       </c>
-      <c r="X10" s="11">
+      <c r="X10" s="9">
         <v>2.81</v>
       </c>
-      <c r="Y10" s="11">
+      <c r="Y10" s="9">
         <v>0.97</v>
       </c>
-      <c r="Z10" s="11">
+      <c r="Z10" s="9">
         <v>1.9</v>
       </c>
       <c r="AA10" s="1">
@@ -1406,40 +1401,40 @@
         <f t="shared" ref="H11" si="2">STDEV(H2:H5,H8)</f>
         <v>390.67544074333716</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11">
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="9">
         <v>0.43</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11">
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9">
         <v>0.04</v>
       </c>
-      <c r="R11" s="11">
+      <c r="R11" s="9">
         <v>0.05</v>
       </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="11">
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="9">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V11" s="11">
+      <c r="V11" s="9">
         <v>0.2</v>
       </c>
-      <c r="W11" s="11">
+      <c r="W11" s="9">
         <v>0.87</v>
       </c>
-      <c r="X11" s="11">
+      <c r="X11" s="9">
         <v>0.93</v>
       </c>
-      <c r="Y11" s="11">
+      <c r="Y11" s="9">
         <v>0.15</v>
       </c>
-      <c r="Z11" s="11">
+      <c r="Z11" s="9">
         <v>0.33</v>
       </c>
       <c r="AA11" s="1">
@@ -1453,7 +1448,7 @@
       <c r="AC11" s="4"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <f>QUARTILE(G2:G8,1)</f>
         <v>39.25</v>
       </c>
@@ -1461,7 +1456,7 @@
       <c r="Y12" s="4"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <f>QUARTILE(G2:G8,3)</f>
         <v>40.799999999999997</v>
       </c>
@@ -1480,15 +1475,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DBB56-BCFF-354A-9EBF-A3C338873D47}">
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1497,10 +1492,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>13</v>
@@ -1518,13 +1513,13 @@
         <v>17</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>32</v>
@@ -1536,13 +1531,13 @@
         <v>34</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>9</v>
@@ -1554,7 +1549,7 @@
         <v>11</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>36</v>
@@ -1571,13 +1566,10 @@
       <c r="AB1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1">
         <v>36.571428571428569</v>
@@ -1585,94 +1577,91 @@
       <c r="C2" s="2">
         <v>2913</v>
       </c>
-      <c r="D2" s="8">
-        <v>32552</v>
+      <c r="D2" s="1">
+        <v>29.632876712328766</v>
       </c>
       <c r="E2" s="1">
-        <v>29.632876712328766</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1">
-        <v>64</v>
+        <v>1.69</v>
       </c>
       <c r="G2" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="H2" s="1">
         <v>41</v>
       </c>
+      <c r="H2" s="2">
+        <v>3830</v>
+      </c>
       <c r="I2" s="2">
-        <v>3830</v>
-      </c>
-      <c r="J2" s="2">
         <v>10</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
         <f>-1.39 + 0.189*B2</f>
         <v>5.5220000000000002</v>
       </c>
-      <c r="M2" s="4">
+      <c r="L2" s="4">
         <f>(-0.1655 + 0.121125*B2)/(0.0028*B2 + 0.798)</f>
         <v>4.7359110236720188</v>
       </c>
+      <c r="M2">
+        <v>3.4</v>
+      </c>
       <c r="N2">
-        <v>3.4</v>
-      </c>
-      <c r="O2">
         <v>5.4</v>
       </c>
+      <c r="O2" s="1">
+        <f t="shared" ref="O2:P10" si="0">M2/K2</f>
+        <v>0.61571894241216951</v>
+      </c>
       <c r="P2" s="1">
-        <f t="shared" ref="P2:Q10" si="0">N2/L2</f>
-        <v>0.61571894241216951</v>
-      </c>
-      <c r="Q2" s="1">
         <f t="shared" si="0"/>
         <v>1.140224124357192</v>
       </c>
-      <c r="R2" s="1">
+      <c r="Q2" s="1">
         <f>2.8/4.35</f>
         <v>0.64367816091954022</v>
       </c>
+      <c r="R2" s="4">
+        <f>1/Q2</f>
+        <v>1.5535714285714286</v>
+      </c>
       <c r="S2" s="4">
-        <f>1/R2</f>
-        <v>1.5535714285714286</v>
-      </c>
-      <c r="T2" s="4">
         <f>1.224*LN(B2)-2.822</f>
         <v>1.5835031695992807</v>
       </c>
-      <c r="U2" s="4">
+      <c r="T2" s="4">
         <f>1.396*LN(B2)-3.359</f>
         <v>1.6655771444122518</v>
       </c>
+      <c r="U2" s="4">
+        <f t="shared" ref="U2:U10" si="1">(LN(M2)-S2)/0.164</f>
+        <v>-2.1934618169339331</v>
+      </c>
       <c r="V2" s="4">
-        <f t="shared" ref="V2:V10" si="1">(LN(N2)-T2)/0.164</f>
-        <v>-2.1934618169339331</v>
-      </c>
-      <c r="W2" s="4">
-        <f t="shared" ref="W2:W10" si="2">(LN(O2)-U2)/0.176</f>
+        <f t="shared" ref="V2:V10" si="2">(LN(N2)-T2)/0.176</f>
         <v>0.11830573385214231</v>
       </c>
+      <c r="W2">
+        <v>4.6420000000000003</v>
+      </c>
       <c r="X2">
-        <v>4.6420000000000003</v>
-      </c>
-      <c r="Y2">
         <v>3.2309999999999999</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AA2" s="1">
         <f>POWER(2.8,3/2)/POWER(4.35,3/2)</f>
         <v>0.51642012869887588</v>
       </c>
-      <c r="AC2" s="1">
-        <f>1/AB2</f>
+      <c r="AB2" s="1">
+        <f>1/AA2</f>
         <v>1.9364078672136715</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1">
         <v>30.571428571428573</v>
@@ -1680,94 +1669,91 @@
       <c r="C3" s="2">
         <v>1503</v>
       </c>
-      <c r="D3" s="8">
-        <v>29056</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="1">
         <v>37.531506849315072</v>
       </c>
-      <c r="H3" s="1">
+      <c r="G3" s="1">
         <v>40</v>
       </c>
+      <c r="H3" s="2">
+        <v>2910</v>
+      </c>
       <c r="I3" s="2">
-        <v>2910</v>
-      </c>
-      <c r="J3" s="2">
         <v>10</v>
       </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
       <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
         <f>-1.39 + 0.189*B3</f>
         <v>4.3880000000000008</v>
       </c>
-      <c r="M3" s="4">
+      <c r="L3" s="4">
         <f>(-0.1655 + 0.121125*B3)/(0.0028*B3 + 0.798)</f>
         <v>4.003467955765375</v>
       </c>
+      <c r="M3">
+        <v>2.6</v>
+      </c>
       <c r="N3">
-        <v>2.6</v>
-      </c>
-      <c r="O3">
         <v>4.5</v>
+      </c>
+      <c r="O3" s="1">
+        <f t="shared" si="0"/>
+        <v>0.59252506836827701</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="0"/>
-        <v>0.59252506836827701</v>
+        <v>1.1240254823370253</v>
       </c>
       <c r="Q3" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1240254823370253</v>
-      </c>
-      <c r="R3" s="1">
         <f xml:space="preserve"> 2.63/3.84</f>
         <v>0.68489583333333337</v>
       </c>
+      <c r="R3" s="4">
+        <f t="shared" ref="R3:R10" si="3">1/Q3</f>
+        <v>1.4600760456273763</v>
+      </c>
       <c r="S3" s="4">
-        <f t="shared" ref="S3:S10" si="3">1/R3</f>
-        <v>1.4600760456273763</v>
-      </c>
-      <c r="T3" s="4">
         <f>1.224*LN(B3)-2.822</f>
         <v>1.3641606199430427</v>
       </c>
-      <c r="U3" s="4">
+      <c r="T3" s="4">
         <f>1.396*LN(B3)-3.359</f>
         <v>1.4154119488892869</v>
       </c>
-      <c r="V3" s="4">
+      <c r="U3" s="4">
         <f t="shared" si="1"/>
         <v>-2.4917632616805268</v>
       </c>
-      <c r="W3" s="4">
+      <c r="V3" s="4">
         <f t="shared" si="2"/>
         <v>0.50378095390333677</v>
       </c>
+      <c r="W3">
+        <v>3.1190000000000002</v>
+      </c>
       <c r="X3">
-        <v>3.1190000000000002</v>
+        <v>2.5609999999999999</v>
       </c>
       <c r="Y3">
-        <v>2.5609999999999999</v>
+        <v>1.8640000000000001</v>
       </c>
       <c r="Z3">
-        <v>1.8640000000000001</v>
-      </c>
-      <c r="AA3">
         <v>1.3959999999999999</v>
       </c>
-      <c r="AB3" s="1">
+      <c r="AA3" s="1">
         <f>POWER(2.63,3/2)/POWER(3.84,3/2)</f>
         <v>0.56680906351658378</v>
       </c>
-      <c r="AC3" s="1">
-        <f t="shared" ref="AC3:AC10" si="4">1/AB3</f>
+      <c r="AB3" s="1">
+        <f t="shared" ref="AB3:AB10" si="4">1/AA3</f>
         <v>1.7642625433612917</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1">
         <v>28</v>
@@ -1775,91 +1761,88 @@
       <c r="C4" s="2">
         <v>1224</v>
       </c>
-      <c r="D4" s="5">
-        <v>28856</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="D4" s="1">
         <v>37.12054794520548</v>
       </c>
-      <c r="H4" s="1">
+      <c r="G4" s="1">
         <v>38</v>
       </c>
+      <c r="H4" s="2">
+        <v>4060</v>
+      </c>
       <c r="I4" s="2">
-        <v>4060</v>
-      </c>
-      <c r="J4" s="2">
         <v>10</v>
       </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
       <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
         <f>-1.39 + 0.189*B4</f>
         <v>3.9020000000000001</v>
       </c>
-      <c r="M4" s="4">
+      <c r="L4" s="4">
         <f>(-0.1655 + 0.121125*B4)/(0.0028*B4 + 0.798)</f>
         <v>3.6809675947056131</v>
       </c>
+      <c r="M4">
+        <v>3.1</v>
+      </c>
       <c r="N4">
-        <v>3.1</v>
-      </c>
-      <c r="O4">
         <v>3.9</v>
+      </c>
+      <c r="O4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.79446437724243979</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="0"/>
-        <v>0.79446437724243979</v>
+        <v>1.0595040297582148</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0595040297582148</v>
-      </c>
-      <c r="R4" s="1">
         <f xml:space="preserve"> 1.79/2.84</f>
         <v>0.63028169014084512</v>
       </c>
-      <c r="S4" s="4">
+      <c r="R4" s="4">
         <f t="shared" si="3"/>
         <v>1.5865921787709496</v>
       </c>
-      <c r="T4" s="4">
+      <c r="S4" s="4">
         <f>1.224*LN(B4)-2.822</f>
         <v>1.2566183204544492</v>
       </c>
-      <c r="U4" s="4">
+      <c r="T4" s="4">
         <f>1.396*LN(B4)-3.359</f>
         <v>1.292757496204584</v>
       </c>
-      <c r="V4" s="4">
+      <c r="U4" s="4">
         <f t="shared" si="1"/>
         <v>-0.76351346928871111</v>
       </c>
-      <c r="W4" s="4">
+      <c r="V4" s="4">
         <f t="shared" si="2"/>
         <v>0.38760827801713976</v>
       </c>
+      <c r="W4">
+        <v>3.3540000000000001</v>
+      </c>
       <c r="X4">
-        <v>3.3540000000000001</v>
-      </c>
-      <c r="Y4">
         <v>2.48</v>
       </c>
-      <c r="AA4">
+      <c r="Z4">
         <v>2.8260000000000001</v>
       </c>
-      <c r="AB4" s="1">
+      <c r="AA4" s="1">
         <f xml:space="preserve"> POWER(1.79,3/2)/POWER(2.84,3/2)</f>
         <v>0.50038241220420621</v>
       </c>
-      <c r="AC4" s="1">
+      <c r="AB4" s="1">
         <f t="shared" si="4"/>
         <v>1.9984715202018326</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1">
         <v>36.714285714285715</v>
@@ -1867,88 +1850,85 @@
       <c r="C5" s="2">
         <v>2891</v>
       </c>
-      <c r="D5" s="5">
-        <v>28013</v>
+      <c r="D5" s="1">
+        <v>41.838356164383562</v>
       </c>
       <c r="E5" s="1">
-        <v>41.838356164383562</v>
+        <v>63</v>
       </c>
       <c r="F5" s="1">
-        <v>63</v>
+        <v>1.75</v>
       </c>
       <c r="G5" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="H5" s="1">
         <v>38.571428571428569</v>
       </c>
+      <c r="H5" s="2">
+        <v>3480</v>
+      </c>
       <c r="I5" s="2">
-        <v>3480</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2">
         <v>0</v>
       </c>
-      <c r="L5">
+      <c r="K5">
         <f>-1.39 + 0.189*B5</f>
         <v>5.5490000000000004</v>
       </c>
-      <c r="M5" s="4">
+      <c r="L5" s="4">
         <f>(-0.1655 + 0.121125*B5)/(0.0028*B5 + 0.798)</f>
         <v>4.753017159350418</v>
       </c>
+      <c r="M5">
+        <v>4.7</v>
+      </c>
       <c r="N5">
-        <v>4.7</v>
-      </c>
-      <c r="O5">
         <v>5</v>
+      </c>
+      <c r="O5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.84699945936204724</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="0"/>
-        <v>0.84699945936204724</v>
+        <v>1.051963380810377</v>
       </c>
       <c r="Q5" s="1">
-        <f t="shared" si="0"/>
-        <v>1.051963380810377</v>
-      </c>
-      <c r="R5" s="1">
         <f xml:space="preserve"> 3.54/4.78</f>
         <v>0.7405857740585774</v>
       </c>
-      <c r="S5" s="4">
+      <c r="R5" s="4">
         <f t="shared" si="3"/>
         <v>1.3502824858757063</v>
       </c>
-      <c r="T5" s="4">
+      <c r="S5" s="4">
         <f>1.224*LN(B5)-2.822</f>
         <v>1.5882751054680453</v>
       </c>
-      <c r="U5" s="4">
+      <c r="T5" s="4">
         <f>1.396*LN(B5)-3.359</f>
         <v>1.6710196464325096</v>
       </c>
-      <c r="V5" s="4">
+      <c r="U5" s="4">
         <f t="shared" si="1"/>
         <v>-0.24824754117092873</v>
       </c>
-      <c r="W5" s="4">
+      <c r="V5" s="4">
         <f t="shared" si="2"/>
         <v>-0.34989621590005271</v>
       </c>
-      <c r="AB5" s="1">
+      <c r="AA5" s="1">
         <f xml:space="preserve"> POWER(3.54,3/2)/POWER(4.78,3/2)</f>
         <v>0.63732807216989762</v>
       </c>
-      <c r="AC5" s="1">
+      <c r="AB5" s="1">
         <f t="shared" si="4"/>
         <v>1.5690506093593537</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1">
         <v>27.285714285714285</v>
@@ -1956,94 +1936,91 @@
       <c r="C6" s="2">
         <v>953</v>
       </c>
-      <c r="D6" s="8">
-        <v>29095</v>
+      <c r="D6" s="1">
+        <v>38.402739726027399</v>
       </c>
       <c r="E6" s="1">
-        <v>38.402739726027399</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1">
-        <v>55</v>
+        <v>1.65</v>
       </c>
       <c r="G6" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="H6" s="1">
         <v>33</v>
       </c>
+      <c r="H6" s="2">
+        <v>1700</v>
+      </c>
       <c r="I6" s="2">
-        <v>1700</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2">
-        <v>8</v>
-      </c>
-      <c r="K6" s="2">
         <v>0</v>
       </c>
-      <c r="L6">
+      <c r="K6">
         <f>-1.39 + 0.189*B6</f>
         <v>3.7670000000000003</v>
       </c>
-      <c r="M6" s="4">
+      <c r="L6" s="4">
         <f>(-0.1655 + 0.121125*B6)/(0.0028*B6 + 0.798)</f>
         <v>3.5904416089400066</v>
       </c>
+      <c r="M6">
+        <v>2.4</v>
+      </c>
       <c r="N6">
-        <v>2.4</v>
-      </c>
-      <c r="O6">
         <v>3.8</v>
+      </c>
+      <c r="O6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.63711176002123693</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="0"/>
-        <v>0.63711176002123693</v>
+        <v>1.058365631274494</v>
       </c>
       <c r="Q6" s="1">
-        <f t="shared" si="0"/>
-        <v>1.058365631274494</v>
-      </c>
-      <c r="R6" s="1">
         <f>1.43/2.15</f>
         <v>0.66511627906976745</v>
       </c>
-      <c r="S6" s="4">
+      <c r="R6" s="4">
         <f t="shared" si="3"/>
         <v>1.5034965034965035</v>
       </c>
-      <c r="T6" s="4">
+      <c r="S6" s="4">
         <f>1.224*LN(B6)-2.822</f>
         <v>1.2249886534853713</v>
       </c>
-      <c r="U6" s="4">
+      <c r="T6" s="4">
         <f>1.396*LN(B6)-3.359</f>
         <v>1.2566831374718772</v>
       </c>
-      <c r="V6" s="4">
+      <c r="U6" s="4">
         <f t="shared" si="1"/>
         <v>-2.1312190008016554</v>
       </c>
-      <c r="W6" s="4">
+      <c r="V6" s="4">
         <f t="shared" si="2"/>
         <v>0.44498823443444757</v>
       </c>
+      <c r="Y6">
+        <v>0.98099999999999998</v>
+      </c>
       <c r="Z6">
-        <v>0.98099999999999998</v>
-      </c>
-      <c r="AA6">
         <v>1.897</v>
       </c>
-      <c r="AB6" s="1">
+      <c r="AA6" s="1">
         <f xml:space="preserve"> POWER(1.43,3/2)/POWER(2.15,3/2)</f>
         <v>0.54243332909261388</v>
       </c>
-      <c r="AC6" s="1">
+      <c r="AB6" s="1">
         <f t="shared" si="4"/>
         <v>1.843544536012945</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1">
         <v>32.571428571428569</v>
@@ -2051,88 +2028,85 @@
       <c r="C7" s="2">
         <v>2133</v>
       </c>
-      <c r="D7" s="5">
-        <v>28039</v>
+      <c r="D7" s="1">
+        <v>41.30684931506849</v>
       </c>
       <c r="E7" s="1">
-        <v>41.30684931506849</v>
+        <v>65</v>
       </c>
       <c r="F7" s="1">
-        <v>65</v>
+        <v>1.6</v>
       </c>
       <c r="G7" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="H7" s="1">
         <v>40</v>
       </c>
+      <c r="H7" s="2">
+        <v>3080</v>
+      </c>
       <c r="I7" s="2">
-        <v>3080</v>
+        <v>10</v>
       </c>
       <c r="J7" s="2">
-        <v>10</v>
-      </c>
-      <c r="K7" s="2">
         <v>2</v>
       </c>
-      <c r="L7">
+      <c r="K7">
         <f>-1.39 + 0.189*B7</f>
         <v>4.766</v>
       </c>
-      <c r="M7" s="4">
+      <c r="L7" s="4">
         <f>(-0.1655 + 0.121125*B7)/(0.0028*B7 + 0.798)</f>
         <v>4.2506908296381978</v>
       </c>
+      <c r="M7">
+        <v>3.5</v>
+      </c>
       <c r="N7">
-        <v>3.5</v>
-      </c>
-      <c r="O7">
         <v>4.4000000000000004</v>
+      </c>
+      <c r="O7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.7343684431389006</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="0"/>
-        <v>0.7343684431389006</v>
+        <v>1.0351258598533526</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0351258598533526</v>
-      </c>
-      <c r="R7" s="1">
         <f>2.02/3.31</f>
         <v>0.61027190332326287</v>
       </c>
-      <c r="S7" s="4">
+      <c r="R7" s="4">
         <f t="shared" si="3"/>
         <v>1.6386138613861385</v>
       </c>
-      <c r="T7" s="4">
+      <c r="S7" s="4">
         <f>1.224*LN(B7)-2.822</f>
         <v>1.4417250273965321</v>
       </c>
-      <c r="U7" s="4">
+      <c r="T7" s="4">
         <f>1.396*LN(B7)-3.359</f>
         <v>1.5038759299391815</v>
       </c>
-      <c r="V7" s="4">
+      <c r="U7" s="4">
         <f t="shared" si="1"/>
         <v>-1.1522076762266098</v>
       </c>
-      <c r="W7" s="4">
+      <c r="V7" s="4">
         <f t="shared" si="2"/>
         <v>-0.12654198303957925</v>
       </c>
-      <c r="AB7" s="1">
+      <c r="AA7" s="1">
         <f xml:space="preserve"> POWER(2.02,3/2)/POWER(3.31,3/2)</f>
         <v>0.47674381065133298</v>
       </c>
-      <c r="AC7" s="1">
+      <c r="AB7" s="1">
         <f t="shared" si="4"/>
         <v>2.0975626272605159</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1">
         <v>39</v>
@@ -2140,94 +2114,91 @@
       <c r="C8" s="2">
         <v>3047</v>
       </c>
-      <c r="D8" s="5">
-        <v>34933</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="1">
         <v>21.043835616438358</v>
       </c>
-      <c r="H8" s="1">
+      <c r="G8" s="1">
         <v>40</v>
       </c>
+      <c r="H8" s="2">
+        <v>3140</v>
+      </c>
       <c r="I8" s="2">
-        <v>3140</v>
-      </c>
-      <c r="J8" s="2">
         <v>9</v>
       </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
       <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
         <f>-1.39 + 0.189*B8</f>
         <v>5.9810000000000008</v>
       </c>
-      <c r="M8" s="4">
+      <c r="L8" s="4">
         <f>(-0.1655 + 0.121125*B8)/(0.0028*B8 + 0.798)</f>
         <v>5.0246638007054676</v>
       </c>
+      <c r="M8">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="N8">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="O8">
         <v>5.6</v>
+      </c>
+      <c r="O8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.38455107841498071</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="0"/>
-        <v>0.38455107841498071</v>
+        <v>1.1145024268516739</v>
       </c>
       <c r="Q8" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1145024268516739</v>
-      </c>
-      <c r="R8" s="1">
         <f>1.94/4.44</f>
         <v>0.43693693693693686</v>
       </c>
-      <c r="S8" s="4">
+      <c r="R8" s="4">
         <f t="shared" si="3"/>
         <v>2.2886597938144333</v>
       </c>
-      <c r="T8" s="4">
+      <c r="S8" s="4">
         <f>1.224*LN(B8)-2.822</f>
         <v>1.6621994548626873</v>
       </c>
-      <c r="U8" s="4">
+      <c r="T8" s="4">
         <f>1.396*LN(B8)-3.359</f>
         <v>1.755332057996986</v>
       </c>
-      <c r="V8" s="4">
+      <c r="U8" s="4">
         <f t="shared" si="1"/>
         <v>-5.0566483654120935</v>
       </c>
-      <c r="W8" s="4">
+      <c r="V8" s="4">
         <f t="shared" si="2"/>
         <v>-0.18503102418115042</v>
       </c>
+      <c r="W8">
+        <v>4.21</v>
+      </c>
       <c r="X8">
-        <v>4.21</v>
+        <v>3.0350000000000001</v>
       </c>
       <c r="Y8">
-        <v>3.0350000000000001</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="Z8">
-        <v>0.85299999999999998</v>
-      </c>
-      <c r="AA8">
         <v>1.4510000000000001</v>
       </c>
-      <c r="AB8" s="1">
+      <c r="AA8" s="1">
         <f xml:space="preserve"> POWER(1.94,3/2)/POWER(4.44,3/2)</f>
         <v>0.28882058261706389</v>
       </c>
-      <c r="AC8" s="1">
+      <c r="AB8" s="1">
         <f t="shared" si="4"/>
         <v>3.4623571178300043</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1">
         <v>30</v>
@@ -2235,94 +2206,91 @@
       <c r="C9" s="2">
         <v>1608</v>
       </c>
-      <c r="D9" s="5">
-        <v>30727</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="1">
         <v>30.975342465753425</v>
       </c>
-      <c r="H9" s="1">
+      <c r="G9" s="1">
         <v>40.714285714285715</v>
       </c>
+      <c r="H9" s="2">
+        <v>2970</v>
+      </c>
       <c r="I9" s="2">
-        <v>2970</v>
-      </c>
-      <c r="J9" s="2">
         <v>10</v>
       </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
       <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
         <f>-1.39 + 0.189*B9</f>
         <v>4.28</v>
       </c>
-      <c r="M9" s="4">
+      <c r="L9" s="4">
         <f>(-0.1655 + 0.121125*B9)/(0.0028*B9 + 0.798)</f>
         <v>3.9322562358276643</v>
       </c>
+      <c r="M9">
+        <v>3</v>
+      </c>
       <c r="N9">
-        <v>3</v>
-      </c>
-      <c r="O9">
         <v>4.2</v>
+      </c>
+      <c r="O9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.7009345794392523</v>
       </c>
       <c r="P9" s="1">
         <f t="shared" si="0"/>
-        <v>0.7009345794392523</v>
+        <v>1.0680890939234484</v>
       </c>
       <c r="Q9" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0680890939234484</v>
-      </c>
-      <c r="R9" s="1">
         <f>1.96/2.32</f>
         <v>0.84482758620689657</v>
       </c>
-      <c r="S9" s="4">
+      <c r="R9" s="4">
         <f t="shared" si="3"/>
         <v>1.1836734693877551</v>
       </c>
-      <c r="T9" s="4">
+      <c r="S9" s="4">
         <f>1.224*LN(B9)-2.822</f>
         <v>1.3410655951544781</v>
       </c>
-      <c r="U9" s="4">
+      <c r="T9" s="4">
         <f>1.396*LN(B9)-3.359</f>
         <v>1.3890715448003688</v>
       </c>
-      <c r="V9" s="4">
+      <c r="U9" s="4">
         <f t="shared" si="1"/>
         <v>-1.4783738200388312</v>
       </c>
-      <c r="W9" s="4">
+      <c r="V9" s="4">
         <f t="shared" si="2"/>
         <v>0.26143738914178394</v>
       </c>
+      <c r="W9">
+        <v>4.1260000000000003</v>
+      </c>
       <c r="X9">
-        <v>4.1260000000000003</v>
+        <v>2.8679999999999999</v>
       </c>
       <c r="Y9">
-        <v>2.8679999999999999</v>
+        <v>1.0720000000000001</v>
       </c>
       <c r="Z9">
-        <v>1.0720000000000001</v>
-      </c>
-      <c r="AA9">
         <v>1.9550000000000001</v>
       </c>
-      <c r="AB9" s="1">
+      <c r="AA9" s="1">
         <f xml:space="preserve"> POWER(1.96,3/2)/POWER(2.32,3/2)</f>
         <v>0.7765190770842213</v>
       </c>
-      <c r="AC9" s="1">
+      <c r="AB9" s="1">
         <f t="shared" si="4"/>
         <v>1.287798367755413</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1">
         <v>28.142857142857142</v>
@@ -2330,90 +2298,87 @@
       <c r="C10" s="2">
         <v>1248</v>
       </c>
-      <c r="D10" s="5">
-        <v>31794</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="1">
         <v>27.936986301369863</v>
       </c>
-      <c r="H10" s="1">
+      <c r="G10" s="1">
         <v>39.714285714285715</v>
       </c>
-      <c r="I10" s="9">
+      <c r="H10" s="7">
         <v>3520</v>
       </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
       <c r="J10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
         <f>-1.39 + 0.189*B10</f>
         <v>3.9290000000000003</v>
       </c>
-      <c r="M10" s="4">
+      <c r="L10" s="4">
         <f>(-0.1655 + 0.121125*B10)/(0.0028*B10 + 0.798)</f>
         <v>3.6990232338373303</v>
       </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
       <c r="N10">
-        <v>2</v>
-      </c>
-      <c r="O10">
         <v>4.0999999999999996</v>
+      </c>
+      <c r="O10" s="1">
+        <f t="shared" si="0"/>
+        <v>0.50903537795876808</v>
       </c>
       <c r="P10" s="1">
         <f t="shared" si="0"/>
-        <v>0.50903537795876808</v>
+        <v>1.1084007157604956</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1084007157604956</v>
-      </c>
-      <c r="R10" s="1">
         <f>0.95/2.01</f>
         <v>0.47263681592039802</v>
       </c>
-      <c r="S10" s="4">
+      <c r="R10" s="4">
         <f t="shared" si="3"/>
         <v>2.1157894736842104</v>
       </c>
-      <c r="T10" s="4">
+      <c r="S10" s="4">
         <f>1.224*LN(B10)-2.822</f>
         <v>1.2628473415315939</v>
       </c>
-      <c r="U10" s="4">
+      <c r="T10" s="4">
         <f>1.396*LN(B10)-3.359</f>
         <v>1.2998618372370139</v>
       </c>
-      <c r="V10" s="4">
+      <c r="U10" s="4">
         <f t="shared" si="1"/>
         <v>-3.473781469339321</v>
       </c>
-      <c r="W10" s="4">
+      <c r="V10" s="4">
         <f t="shared" si="2"/>
         <v>0.63139282087072834</v>
       </c>
+      <c r="W10">
+        <v>3.6280000000000001</v>
+      </c>
       <c r="X10">
-        <v>3.6280000000000001</v>
-      </c>
-      <c r="Y10">
         <v>2.8460000000000001</v>
       </c>
-      <c r="AB10" s="1">
+      <c r="AA10" s="1">
         <f xml:space="preserve"> POWER(0.95,3/2)/POWER(2.01,3/2)</f>
         <v>0.3249311306864211</v>
       </c>
-      <c r="AC10" s="1">
+      <c r="AB10" s="1">
         <f t="shared" si="4"/>
         <v>3.0775752322884156</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="U11" s="4"/>
       <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2426,89 +2391,88 @@
         <v>1946.6666666666667</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1">
+        <f>AVERAGE(E10,E9,E8,E7,E6,E5,E4,E3,E2)</f>
+        <v>61.75</v>
+      </c>
       <c r="F12" s="1">
         <f>AVERAGE(F10,F9,F8,F7,F6,F5,F4,F3,F2)</f>
-        <v>61.75</v>
+        <v>1.6724999999999999</v>
       </c>
       <c r="G12" s="1">
-        <f>AVERAGE(G10,G9,G8,G7,G6,G5,G4,G3,G2)</f>
-        <v>1.6724999999999999</v>
+        <f>MEDIAN(G2:G10)</f>
+        <v>40</v>
       </c>
       <c r="H12" s="1">
-        <f>MEDIAN(H2:H10)</f>
-        <v>40</v>
-      </c>
-      <c r="I12" s="1">
-        <f>AVERAGE(I10,I9,I8,I7,I6,I5,I4,I3,I2)</f>
+        <f>AVERAGE(H10,H9,H8,H7,H6,H5,H4,H3,H2)</f>
         <v>3187.7777777777778</v>
       </c>
+      <c r="K12" s="1">
+        <f t="shared" ref="K12:R12" si="5">AVERAGE(K10,K9,K8,K7,K6,K5,K4,K3,K2)</f>
+        <v>4.6759999999999993</v>
+      </c>
       <c r="L12" s="1">
-        <f t="shared" ref="L12:S12" si="5">AVERAGE(L10,L9,L8,L7,L6,L5,L4,L3,L2)</f>
-        <v>4.6759999999999993</v>
+        <f t="shared" si="5"/>
+        <v>4.1856043824935654</v>
       </c>
       <c r="M12" s="1">
         <f t="shared" si="5"/>
-        <v>4.1856043824935654</v>
+        <v>3.0000000000000004</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" si="5"/>
-        <v>3.0000000000000004</v>
+        <v>4.5444444444444443</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" si="5"/>
-        <v>4.5444444444444443</v>
+        <v>0.64618989848423036</v>
       </c>
       <c r="P12" s="1">
         <f t="shared" si="5"/>
-        <v>0.64618989848423036</v>
+        <v>1.0844667494362525</v>
       </c>
       <c r="Q12" s="1">
         <f t="shared" si="5"/>
-        <v>1.0844667494362525</v>
+        <v>0.63658121998995087</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="5"/>
-        <v>0.63658121998995087</v>
-      </c>
-      <c r="S12" s="1">
-        <f t="shared" si="5"/>
         <v>1.6311950267349447</v>
+      </c>
+      <c r="U12" s="1">
+        <f>AVERAGE(U2:U10)</f>
+        <v>-2.1099129356547346</v>
       </c>
       <c r="V12" s="1">
         <f>AVERAGE(V2:V10)</f>
-        <v>-2.1099129356547346</v>
+        <v>0.18733824301097737</v>
       </c>
       <c r="W12" s="1">
-        <f>AVERAGE(W2:W10)</f>
-        <v>0.18733824301097737</v>
+        <f t="shared" ref="W12:Z12" si="6">AVERAGE(W2:W10)</f>
+        <v>3.8465000000000007</v>
       </c>
       <c r="X12" s="1">
-        <f t="shared" ref="X12:AA12" si="6">AVERAGE(X2:X10)</f>
-        <v>3.8465000000000007</v>
+        <f t="shared" si="6"/>
+        <v>2.8368333333333333</v>
       </c>
       <c r="Y12" s="1">
         <f t="shared" si="6"/>
-        <v>2.8368333333333333</v>
+        <v>1.1925000000000001</v>
       </c>
       <c r="Z12" s="1">
         <f t="shared" si="6"/>
-        <v>1.1925000000000001</v>
+        <v>1.905</v>
       </c>
       <c r="AA12" s="1">
-        <f t="shared" si="6"/>
-        <v>1.905</v>
+        <f>AVERAGE(AA2:AA10)</f>
+        <v>0.51448751185791297</v>
       </c>
       <c r="AB12" s="1">
         <f>AVERAGE(AB2:AB10)</f>
-        <v>0.51448751185791297</v>
-      </c>
-      <c r="AC12" s="1">
-        <f>AVERAGE(AC2:AC10)</f>
         <v>2.1152256023648266</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2521,98 +2485,97 @@
         <v>820.08459929448748</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1">
+        <f>STDEV(E10,E9,E8,E7,E6,E5,E4,E3,E2)</f>
+        <v>4.5734742446707477</v>
+      </c>
       <c r="F13" s="1">
         <f>STDEV(F10,F9,F8,F7,F6,F5,F4,F3,F2)</f>
-        <v>4.5734742446707477</v>
-      </c>
-      <c r="G13" s="1">
-        <f>STDEV(G10,G9,G8,G7,G6,G5,G4,G3,G2)</f>
         <v>6.3442887702247569E-2</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1">
-        <f>STDEV(I10,I9,I8,I7,I6,I5,I4,I3,I2)</f>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <f>STDEV(H10,H9,H8,H7,H6,H5,H4,H3,H2)</f>
         <v>681.99666014170771</v>
       </c>
+      <c r="K13" s="1">
+        <f t="shared" ref="K13:R13" si="7">STDEV(K10,K9,K8,K7,K6,K5,K4,K3,K2)</f>
+        <v>0.8225034954333057</v>
+      </c>
       <c r="L13" s="1">
-        <f t="shared" ref="L13:S13" si="7">STDEV(L10,L9,L8,L7,L6,L5,L4,L3,L2)</f>
-        <v>0.8225034954333057</v>
+        <f t="shared" si="7"/>
+        <v>0.5333911324907904</v>
       </c>
       <c r="M13" s="1">
         <f t="shared" si="7"/>
-        <v>0.5333911324907904</v>
+        <v>0.8154753215150029</v>
       </c>
       <c r="N13" s="1">
         <f t="shared" si="7"/>
-        <v>0.8154753215150029</v>
+        <v>0.64828834462589013</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" si="7"/>
-        <v>0.64828834462589013</v>
+        <v>0.14328262152225268</v>
       </c>
       <c r="P13" s="1">
         <f t="shared" si="7"/>
-        <v>0.14328262152225268</v>
+        <v>3.7437248444193376E-2</v>
       </c>
       <c r="Q13" s="1">
         <f t="shared" si="7"/>
-        <v>3.7437248444193376E-2</v>
+        <v>0.12492492042253006</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="7"/>
-        <v>0.12492492042253006</v>
-      </c>
-      <c r="S13" s="1">
-        <f t="shared" si="7"/>
         <v>0.35354235823764896</v>
+      </c>
+      <c r="U13" s="1">
+        <f>STDEV(U2:U10)</f>
+        <v>1.4701726806808169</v>
       </c>
       <c r="V13" s="1">
         <f>STDEV(V2:V10)</f>
-        <v>1.4701726806808169</v>
+        <v>0.34275880084821458</v>
       </c>
       <c r="W13" s="1">
-        <f>STDEV(W2:W10)</f>
-        <v>0.34275880084821458</v>
+        <f t="shared" ref="W13:Z13" si="8">STDEV(W2:W10)</f>
+        <v>0.5766502406138353</v>
       </c>
       <c r="X13" s="1">
-        <f t="shared" ref="X13:AA13" si="8">STDEV(X2:X10)</f>
-        <v>0.5766502406138353</v>
+        <f t="shared" si="8"/>
+        <v>0.28252675389539073</v>
       </c>
       <c r="Y13" s="1">
         <f t="shared" si="8"/>
-        <v>0.28252675389539073</v>
+        <v>0.45659062627259406</v>
       </c>
       <c r="Z13" s="1">
         <f t="shared" si="8"/>
-        <v>0.45659062627259406</v>
+        <v>0.57358565184286148</v>
       </c>
       <c r="AA13" s="1">
-        <f t="shared" si="8"/>
-        <v>0.57358565184286148</v>
+        <f>STDEV(AA2:AA10)</f>
+        <v>0.14821998782312124</v>
       </c>
       <c r="AB13" s="1">
         <f>STDEV(AB2:AB10)</f>
-        <v>0.14821998782312124</v>
-      </c>
-      <c r="AC13" s="1">
-        <f>STDEV(AC2:AC10)</f>
         <v>0.70415978576656846</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="H14" s="6">
-        <f>QUARTILE(H2:H10,1)</f>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="G14" s="5">
+        <f>QUARTILE(G2:G10,1)</f>
         <v>38.571428571428569</v>
       </c>
-      <c r="X14" s="2"/>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="H15" s="6">
-        <f>QUARTILE(H2:H10,3)</f>
+      <c r="W14" s="2"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="G15" s="5">
+        <f>QUARTILE(G2:G10,3)</f>
         <v>40</v>
       </c>
-      <c r="X15" s="2"/>
+      <c r="W15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Dataset_S1.xlsx
+++ b/Dataset_S1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inmav/Desktop/Inma/IDIBAPS/CoA_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB334336-3FFE-EB48-AAB5-5CB25B875A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C45A266-5C1C-EC4A-8DAB-DC33C58AC9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38040" yWindow="760" windowWidth="34560" windowHeight="19840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="7" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
   <si>
     <t>GA</t>
   </si>
@@ -57,9 +57,6 @@
     <t>Std</t>
   </si>
   <si>
-    <t>Maternal age</t>
-  </si>
-  <si>
     <t>ln_predicted_ist</t>
   </si>
   <si>
@@ -70,33 +67,6 @@
   </si>
   <si>
     <t>z-score_da</t>
-  </si>
-  <si>
-    <t>Maternal weight</t>
-  </si>
-  <si>
-    <t>Maternal height</t>
-  </si>
-  <si>
-    <t>GA at delivery</t>
-  </si>
-  <si>
-    <t>Birthweight</t>
-  </si>
-  <si>
-    <t>Apgar</t>
-  </si>
-  <si>
-    <t>Mode of birth</t>
-  </si>
-  <si>
-    <t>Cesarea</t>
-  </si>
-  <si>
-    <t>Eutocic</t>
-  </si>
-  <si>
-    <t>Instrumental</t>
   </si>
   <si>
     <t>ID</t>
@@ -190,7 +160,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,13 +171,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -251,15 +214,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -575,16 +536,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6054E5-5EC8-DD45-92F4-CB319141F7D3}">
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -592,85 +549,64 @@
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>32</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>42</v>
       </c>
       <c r="B2">
         <v>30.57</v>
@@ -678,88 +614,67 @@
       <c r="C2">
         <v>1358</v>
       </c>
-      <c r="D2">
-        <v>30.71</v>
-      </c>
-      <c r="E2" s="8">
-        <v>63</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1.68</v>
-      </c>
-      <c r="G2">
-        <v>41</v>
-      </c>
-      <c r="H2">
-        <v>2595</v>
-      </c>
-      <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="9">
+      <c r="D2" s="7">
         <v>4.3899999999999997</v>
       </c>
-      <c r="L2" s="9">
+      <c r="E2" s="7">
         <v>4</v>
       </c>
+      <c r="F2" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="G2" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0.98</v>
+      </c>
+      <c r="I2" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="K2" s="8">
+        <v>1.1767068300000001</v>
+      </c>
+      <c r="L2" s="8">
+        <v>1.3640000000000001</v>
+      </c>
       <c r="M2" s="8">
-        <v>4.3</v>
+        <v>1.415</v>
       </c>
       <c r="N2" s="8">
-        <v>4.2</v>
-      </c>
-      <c r="O2" s="9">
-        <v>0.98</v>
-      </c>
-      <c r="P2" s="9">
-        <v>1.05</v>
-      </c>
-      <c r="Q2" s="9">
-        <v>0.85</v>
-      </c>
-      <c r="R2" s="10">
-        <v>1.1767068300000001</v>
-      </c>
-      <c r="S2" s="10">
-        <v>1.3640000000000001</v>
-      </c>
-      <c r="T2" s="10">
-        <v>1.415</v>
-      </c>
-      <c r="U2" s="10">
         <v>0.57599999999999996</v>
       </c>
-      <c r="V2" s="10">
+      <c r="O2" s="8">
         <v>0.112</v>
       </c>
-      <c r="W2" s="8">
+      <c r="P2" s="6">
         <v>3.8159999999999998</v>
       </c>
-      <c r="X2" s="8">
+      <c r="Q2" s="6">
         <v>2.8370000000000002</v>
       </c>
-      <c r="Y2" s="8">
+      <c r="R2" s="6">
         <v>0.82799999999999996</v>
       </c>
-      <c r="Z2" s="8">
+      <c r="S2" s="6">
         <v>2.0779999999999998</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="T2" s="1">
         <f>POWER(2.49,3/2)/POWER(2.93,3/2)</f>
         <v>0.78342529554977092</v>
       </c>
-      <c r="AB2" s="1">
-        <f>1/AA2</f>
+      <c r="U2" s="1">
+        <f>1/T2</f>
         <v>1.2764458917531469</v>
       </c>
-      <c r="AC2" s="4"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="V2" s="4"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>30.71</v>
@@ -767,88 +682,67 @@
       <c r="C3">
         <v>1807</v>
       </c>
-      <c r="D3">
-        <v>29.85</v>
-      </c>
-      <c r="E3">
-        <v>55</v>
-      </c>
-      <c r="F3">
-        <v>1.64</v>
-      </c>
-      <c r="G3">
-        <v>41.1</v>
-      </c>
-      <c r="H3">
-        <v>3598</v>
-      </c>
-      <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="9">
+      <c r="D3" s="7">
         <v>4.41</v>
       </c>
-      <c r="L3" s="9">
+      <c r="E3" s="7">
         <v>4.0199999999999996</v>
       </c>
+      <c r="F3" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="G3" s="6">
+        <v>4</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="K3" s="8">
+        <v>1.10747664</v>
+      </c>
+      <c r="L3" s="8">
+        <v>1.37</v>
+      </c>
       <c r="M3" s="8">
-        <v>4.3</v>
+        <v>1.4219999999999999</v>
       </c>
       <c r="N3" s="8">
-        <v>4</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0.97</v>
-      </c>
-      <c r="P3" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>0.9</v>
-      </c>
-      <c r="R3" s="10">
-        <v>1.10747664</v>
-      </c>
-      <c r="S3" s="10">
-        <v>1.37</v>
-      </c>
-      <c r="T3" s="10">
-        <v>1.4219999999999999</v>
-      </c>
-      <c r="U3" s="10">
         <v>0.54200000000000004</v>
       </c>
-      <c r="V3" s="10">
+      <c r="O3" s="8">
         <v>-0.20100000000000001</v>
       </c>
-      <c r="W3" s="8">
+      <c r="P3" s="6">
         <v>2.9910000000000001</v>
       </c>
-      <c r="X3" s="8">
+      <c r="Q3" s="6">
         <v>2.387</v>
       </c>
-      <c r="Y3" s="8">
+      <c r="R3" s="6">
         <v>1.012</v>
       </c>
-      <c r="Z3" s="8">
+      <c r="S3" s="6">
         <v>2.2589999999999999</v>
       </c>
-      <c r="AA3" s="1">
+      <c r="T3" s="1">
         <f>POWER(2.14,3/2)/POWER(2.37,3/2)</f>
         <v>0.85802144196613073</v>
       </c>
-      <c r="AB3" s="1">
-        <f t="shared" ref="AB3:AB8" si="0">1/AA3</f>
+      <c r="U3" s="1">
+        <f t="shared" ref="U3:U8" si="0">1/T3</f>
         <v>1.165472039613054</v>
       </c>
-      <c r="AC3" s="4"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="V3" s="4"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>30.43</v>
@@ -856,88 +750,67 @@
       <c r="C4">
         <v>1562</v>
       </c>
-      <c r="D4">
-        <v>35.020000000000003</v>
-      </c>
-      <c r="E4">
-        <v>55</v>
-      </c>
-      <c r="F4">
-        <v>1.53</v>
-      </c>
-      <c r="G4">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="H4">
-        <v>3230</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="9">
+      <c r="D4" s="7">
         <v>4.3600000000000003</v>
       </c>
-      <c r="L4" s="9">
+      <c r="E4" s="7">
         <v>3.99</v>
       </c>
+      <c r="F4" s="6">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="I4" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.95</v>
+      </c>
+      <c r="K4" s="8">
+        <v>1.0562913899999999</v>
+      </c>
+      <c r="L4" s="8">
+        <v>1.3580000000000001</v>
+      </c>
       <c r="M4" s="8">
-        <v>4</v>
+        <v>1.409</v>
       </c>
       <c r="N4" s="8">
-        <v>4.2</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0.92</v>
-      </c>
-      <c r="P4" s="9">
-        <v>1.05</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0.95</v>
-      </c>
-      <c r="R4" s="10">
-        <v>1.0562913899999999</v>
-      </c>
-      <c r="S4" s="10">
-        <v>1.3580000000000001</v>
-      </c>
-      <c r="T4" s="10">
-        <v>1.409</v>
-      </c>
-      <c r="U4" s="10">
         <v>0.17</v>
       </c>
-      <c r="V4" s="10">
+      <c r="O4" s="8">
         <v>0.14899999999999999</v>
       </c>
-      <c r="W4" s="8">
+      <c r="P4" s="6">
         <v>4.46</v>
       </c>
-      <c r="X4" s="8">
+      <c r="Q4" s="6">
         <v>4.7220000000000004</v>
       </c>
-      <c r="Y4" s="8">
+      <c r="R4" s="6">
         <v>0.85299999999999998</v>
       </c>
-      <c r="Z4" s="8">
+      <c r="S4" s="6">
         <v>1.4590000000000001</v>
       </c>
-      <c r="AA4" s="1">
+      <c r="T4" s="1">
         <f>POWER(3.02,3/2)/POWER(3.19,3/2)</f>
         <v>0.921137344797334</v>
       </c>
-      <c r="AB4" s="1">
+      <c r="U4" s="1">
         <f t="shared" si="0"/>
         <v>1.0856144370305789</v>
       </c>
-      <c r="AC4" s="4"/>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="V4" s="4"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>33</v>
@@ -945,88 +818,67 @@
       <c r="C5">
         <v>2195</v>
       </c>
-      <c r="D5">
-        <v>39.31</v>
-      </c>
-      <c r="E5" s="8">
-        <v>81</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1.59</v>
-      </c>
-      <c r="G5">
-        <v>40.1</v>
-      </c>
-      <c r="H5">
-        <v>3045</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="9">
+      <c r="D5" s="7">
         <v>4.8499999999999996</v>
       </c>
-      <c r="L5" s="9">
+      <c r="E5" s="7">
         <v>4.3</v>
       </c>
+      <c r="F5" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="G5" s="6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.02</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="K5" s="8">
+        <v>1.1791666700000001</v>
+      </c>
+      <c r="L5" s="8">
+        <v>1.458</v>
+      </c>
       <c r="M5" s="8">
-        <v>4.2</v>
+        <v>1.522</v>
       </c>
       <c r="N5" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0.87</v>
-      </c>
-      <c r="P5" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0.85</v>
-      </c>
-      <c r="R5" s="10">
-        <v>1.1791666700000001</v>
-      </c>
-      <c r="S5" s="10">
-        <v>1.458</v>
-      </c>
-      <c r="T5" s="10">
-        <v>1.522</v>
-      </c>
-      <c r="U5" s="10">
         <v>-0.13800000000000001</v>
       </c>
-      <c r="V5" s="10">
+      <c r="O5" s="8">
         <v>-0.23</v>
       </c>
-      <c r="W5" s="8">
+      <c r="P5" s="6">
         <v>3.714</v>
       </c>
-      <c r="X5" s="8">
+      <c r="Q5" s="6">
         <v>2.4220000000000002</v>
       </c>
-      <c r="Y5" s="8">
+      <c r="R5" s="6">
         <v>1.25</v>
       </c>
-      <c r="Z5" s="8">
+      <c r="S5" s="6">
         <v>2.266</v>
       </c>
-      <c r="AA5" s="1">
+      <c r="T5" s="1">
         <f>POWER(2.4,3/2)/POWER(2.83,3/2)</f>
         <v>0.78097513936203178</v>
       </c>
-      <c r="AB5" s="1">
+      <c r="U5" s="1">
         <f t="shared" si="0"/>
         <v>1.280450490161424</v>
       </c>
-      <c r="AC5" s="4"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="V5" s="4"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>32.14</v>
@@ -1034,82 +886,67 @@
       <c r="C6">
         <v>1764</v>
       </c>
-      <c r="D6">
-        <v>30.87</v>
-      </c>
-      <c r="G6">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="H6">
-        <v>3080</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="9">
+      <c r="D6" s="7">
         <v>4.68</v>
       </c>
-      <c r="L6" s="9">
+      <c r="E6" s="7">
         <v>4.2</v>
       </c>
+      <c r="F6" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G6" s="6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="K6" s="8">
+        <v>1.0703517600000001</v>
+      </c>
+      <c r="L6" s="8">
+        <v>1.425</v>
+      </c>
       <c r="M6" s="8">
-        <v>4.0999999999999996</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="N6" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="O6" s="9">
-        <v>0.88</v>
-      </c>
-      <c r="P6" s="9">
-        <v>1.05</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0.93</v>
-      </c>
-      <c r="R6" s="10">
-        <v>1.0703517600000001</v>
-      </c>
-      <c r="S6" s="10">
-        <v>1.425</v>
-      </c>
-      <c r="T6" s="10">
-        <v>1.4850000000000001</v>
-      </c>
-      <c r="U6" s="10">
         <v>-8.7999999999999995E-2</v>
       </c>
-      <c r="V6" s="10">
+      <c r="O6" s="8">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="W6" s="8">
+      <c r="P6" s="6">
         <v>2.7589999999999999</v>
       </c>
-      <c r="X6" s="8">
+      <c r="Q6" s="6">
         <v>1.7949999999999999</v>
       </c>
-      <c r="Y6" s="8">
+      <c r="R6" s="6">
         <v>0.83199999999999996</v>
       </c>
-      <c r="Z6" s="8">
+      <c r="S6" s="6">
         <v>1.7509999999999999</v>
       </c>
-      <c r="AA6" s="1">
+      <c r="T6" s="1">
         <f>POWER(3.98,3/2)/POWER(4.26,3/2)</f>
         <v>0.90304669902872914</v>
       </c>
-      <c r="AB6" s="1">
+      <c r="U6" s="1">
         <f t="shared" si="0"/>
         <v>1.1073624443514924</v>
       </c>
-      <c r="AC6" s="4"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="V6" s="4"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>37.43</v>
@@ -1117,82 +954,67 @@
       <c r="C7">
         <v>2902</v>
       </c>
-      <c r="D7">
-        <v>35.950000000000003</v>
-      </c>
-      <c r="G7">
-        <v>40.6</v>
-      </c>
-      <c r="H7">
-        <v>3415</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="9">
+      <c r="D7" s="7">
         <v>5.68</v>
       </c>
-      <c r="L7" s="9">
+      <c r="E7" s="7">
         <v>4.84</v>
       </c>
+      <c r="F7" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1.1059431500000001</v>
+      </c>
+      <c r="L7" s="8">
+        <v>1.6120000000000001</v>
+      </c>
       <c r="M7" s="8">
-        <v>4.3</v>
+        <v>1.698</v>
       </c>
       <c r="N7" s="8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="O7" s="9">
-        <v>0.76</v>
-      </c>
-      <c r="P7" s="9">
-        <v>1.05</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0.9</v>
-      </c>
-      <c r="R7" s="10">
-        <v>1.1059431500000001</v>
-      </c>
-      <c r="S7" s="10">
-        <v>1.6120000000000001</v>
-      </c>
-      <c r="T7" s="10">
-        <v>1.698</v>
-      </c>
-      <c r="U7" s="10">
         <v>-0.93500000000000005</v>
       </c>
-      <c r="V7" s="10">
+      <c r="O7" s="8">
         <v>-0.39100000000000001</v>
       </c>
-      <c r="W7" s="8">
+      <c r="P7" s="6">
         <v>4.9649999999999999</v>
       </c>
-      <c r="X7" s="8">
+      <c r="Q7" s="6">
         <v>3.0790000000000002</v>
       </c>
-      <c r="Y7" s="8">
+      <c r="R7" s="6">
         <v>1.012</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="S7" s="6">
         <v>1.9510000000000001</v>
       </c>
-      <c r="AA7" s="1">
+      <c r="T7" s="1">
         <f>POWER(3.87,3/2)/POWER(4.28,3/2)</f>
         <v>0.85980663862047302</v>
       </c>
-      <c r="AB7" s="1">
+      <c r="U7" s="1">
         <f t="shared" si="0"/>
         <v>1.1630521969503071</v>
       </c>
-      <c r="AC7" s="4"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="V7" s="4"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>28.29</v>
@@ -1200,101 +1022,83 @@
       <c r="C8">
         <v>1242</v>
       </c>
-      <c r="E8">
-        <v>88</v>
-      </c>
-      <c r="F8">
-        <v>1.64</v>
-      </c>
-      <c r="G8">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="H8">
-        <v>3450</v>
-      </c>
-      <c r="I8">
-        <v>9</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="9">
+      <c r="D8" s="7">
         <v>3.96</v>
       </c>
-      <c r="L8" s="9">
+      <c r="E8" s="7">
         <v>3.72</v>
       </c>
+      <c r="F8" s="6">
+        <v>4</v>
+      </c>
+      <c r="G8" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1.01</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1.09375</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1.2689999999999999</v>
+      </c>
       <c r="M8" s="8">
-        <v>4</v>
+        <v>1.3069999999999999</v>
       </c>
       <c r="N8" s="8">
-        <v>3.7</v>
-      </c>
-      <c r="O8" s="9">
-        <v>1.01</v>
-      </c>
-      <c r="P8" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0.91</v>
-      </c>
-      <c r="R8" s="10">
-        <v>1.09375</v>
-      </c>
-      <c r="S8" s="10">
-        <v>1.2689999999999999</v>
-      </c>
-      <c r="T8" s="10">
-        <v>1.3069999999999999</v>
-      </c>
-      <c r="U8" s="10">
         <v>0.71399999999999997</v>
       </c>
-      <c r="V8" s="10">
+      <c r="O8" s="8">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="W8" s="8">
+      <c r="P8" s="6">
         <v>2.7189999999999999</v>
       </c>
-      <c r="X8" s="8">
+      <c r="Q8" s="6">
         <v>2.4529999999999998</v>
       </c>
-      <c r="Y8" s="8">
+      <c r="R8" s="6">
         <v>0.97</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="S8" s="6">
         <v>1.532</v>
       </c>
-      <c r="AA8" s="1">
+      <c r="T8" s="1">
         <f>POWER(1.92,3/2)/POWER(2.1,3/2)</f>
         <v>0.87422435425601375</v>
       </c>
-      <c r="AB8" s="1">
+      <c r="U8" s="1">
         <f t="shared" si="0"/>
         <v>1.1438711300270563</v>
       </c>
-      <c r="AC8" s="4"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="K9" s="8"/>
+      <c r="V8" s="4"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1306,73 +1110,53 @@
         <f>AVERAGE(C2:C5,C6,C7,C8)</f>
         <v>1832.8571428571429</v>
       </c>
-      <c r="D10" s="1">
-        <f>AVERAGE(D2:D5,D6,D7,D8)</f>
-        <v>33.618333333333339</v>
-      </c>
-      <c r="E10">
-        <f>AVERAGE(E2:E8)</f>
-        <v>68.400000000000006</v>
-      </c>
-      <c r="F10">
-        <f>AVERAGE(F2:F8)</f>
-        <v>1.6160000000000001</v>
-      </c>
-      <c r="G10" s="1">
-        <f>MEDIAN(G2:G8)</f>
-        <v>40.1</v>
-      </c>
-      <c r="H10" s="1">
-        <f t="shared" ref="H10" si="1">AVERAGE(H2:H8)</f>
-        <v>3201.8571428571427</v>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7">
         <v>4.17</v>
       </c>
-      <c r="N10" s="9">
+      <c r="G10" s="7">
         <v>4.29</v>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9">
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7">
         <v>0.9</v>
       </c>
-      <c r="R10" s="9">
+      <c r="K10" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="9">
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="7">
         <v>0.12</v>
       </c>
-      <c r="V10" s="9">
+      <c r="O10" s="7">
         <v>-0.08</v>
       </c>
-      <c r="W10" s="9">
+      <c r="P10" s="7">
         <v>3.63</v>
       </c>
-      <c r="X10" s="9">
+      <c r="Q10" s="7">
         <v>2.81</v>
       </c>
-      <c r="Y10" s="9">
+      <c r="R10" s="7">
         <v>0.97</v>
       </c>
-      <c r="Z10" s="9">
+      <c r="S10" s="7">
         <v>1.9</v>
       </c>
-      <c r="AA10" s="1">
-        <f>AVERAGE(AA2:AA8)</f>
+      <c r="T10" s="1">
+        <f>AVERAGE(T2:T8)</f>
         <v>0.85437670194006898</v>
       </c>
-      <c r="AB10" s="1">
-        <f>AVERAGE(AB2:AB8)</f>
+      <c r="U10" s="1">
+        <f>AVERAGE(U2:U8)</f>
         <v>1.1746098042695798</v>
       </c>
-      <c r="AC10" s="4"/>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="V10" s="4"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1384,106 +1168,81 @@
         <f>STDEV(C2:C5,C6,C7,C8)</f>
         <v>566.80226668901889</v>
       </c>
-      <c r="D11" s="1">
-        <f>STDEV(D2:D5,D6,D7,D8)</f>
-        <v>3.7418841065252715</v>
-      </c>
-      <c r="E11" s="1">
-        <f>STDEV(E2:E5,E8)</f>
-        <v>15.257784898208527</v>
-      </c>
-      <c r="F11" s="1">
-        <f>STDEV(F2:F5,F8)</f>
-        <v>5.7706152185013973E-2</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1">
-        <f t="shared" ref="H11" si="2">STDEV(H2:H5,H8)</f>
-        <v>390.67544074333716</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N11" s="9">
+      <c r="G11" s="7">
         <v>0.43</v>
       </c>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9">
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7">
         <v>0.04</v>
       </c>
-      <c r="R11" s="9">
+      <c r="K11" s="7">
         <v>0.05</v>
       </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="9">
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V11" s="9">
+      <c r="O11" s="7">
         <v>0.2</v>
       </c>
-      <c r="W11" s="9">
+      <c r="P11" s="7">
         <v>0.87</v>
       </c>
-      <c r="X11" s="9">
+      <c r="Q11" s="7">
         <v>0.93</v>
       </c>
-      <c r="Y11" s="9">
+      <c r="R11" s="7">
         <v>0.15</v>
       </c>
-      <c r="Z11" s="9">
+      <c r="S11" s="7">
         <v>0.33</v>
       </c>
-      <c r="AA11" s="1">
-        <f>STDEV(AA2:AA8)</f>
+      <c r="T11" s="1">
+        <f>STDEV(T2:T8)</f>
         <v>5.4289871912493369E-2</v>
       </c>
-      <c r="AB11" s="1">
-        <f>STDEV(AB2:AB8)</f>
+      <c r="U11" s="1">
+        <f>STDEV(U2:U8)</f>
         <v>7.6569320916873213E-2</v>
       </c>
-      <c r="AC11" s="4"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="G12" s="5">
-        <f>QUARTILE(G2:G8,1)</f>
-        <v>39.25</v>
-      </c>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="G13" s="5">
-        <f>QUARTILE(G2:G8,3)</f>
-        <v>40.799999999999997</v>
-      </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
+      <c r="V11" s="4"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DBB56-BCFF-354A-9EBF-A3C338873D47}">
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="14" max="14" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1492,84 +1251,63 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>12</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>22</v>
       </c>
       <c r="B2" s="1">
         <v>36.571428571428569</v>
@@ -1577,91 +1315,70 @@
       <c r="C2" s="2">
         <v>2913</v>
       </c>
-      <c r="D2" s="1">
-        <v>29.632876712328766</v>
-      </c>
-      <c r="E2" s="1">
-        <v>64</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="G2" s="1">
-        <v>41</v>
-      </c>
-      <c r="H2" s="2">
-        <v>3830</v>
-      </c>
-      <c r="I2" s="2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="D2">
         <f>-1.39 + 0.189*B2</f>
         <v>5.5220000000000002</v>
       </c>
-      <c r="L2" s="4">
+      <c r="E2" s="4">
         <f>(-0.1655 + 0.121125*B2)/(0.0028*B2 + 0.798)</f>
         <v>4.7359110236720188</v>
       </c>
-      <c r="M2">
+      <c r="F2">
         <v>3.4</v>
       </c>
-      <c r="N2">
+      <c r="G2">
         <v>5.4</v>
       </c>
-      <c r="O2" s="1">
-        <f t="shared" ref="O2:P10" si="0">M2/K2</f>
+      <c r="H2" s="1">
+        <f t="shared" ref="H2:I10" si="0">F2/D2</f>
         <v>0.61571894241216951</v>
       </c>
-      <c r="P2" s="1">
+      <c r="I2" s="1">
         <f t="shared" si="0"/>
         <v>1.140224124357192</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="J2" s="1">
         <f>2.8/4.35</f>
         <v>0.64367816091954022</v>
       </c>
-      <c r="R2" s="4">
-        <f>1/Q2</f>
+      <c r="K2" s="4">
+        <f>1/J2</f>
         <v>1.5535714285714286</v>
       </c>
-      <c r="S2" s="4">
+      <c r="L2" s="4">
         <f>1.224*LN(B2)-2.822</f>
         <v>1.5835031695992807</v>
       </c>
-      <c r="T2" s="4">
+      <c r="M2" s="4">
         <f>1.396*LN(B2)-3.359</f>
         <v>1.6655771444122518</v>
       </c>
-      <c r="U2" s="4">
-        <f t="shared" ref="U2:U10" si="1">(LN(M2)-S2)/0.164</f>
+      <c r="N2" s="4">
+        <f t="shared" ref="N2:N10" si="1">(LN(F2)-L2)/0.164</f>
         <v>-2.1934618169339331</v>
       </c>
-      <c r="V2" s="4">
-        <f t="shared" ref="V2:V10" si="2">(LN(N2)-T2)/0.176</f>
+      <c r="O2" s="4">
+        <f t="shared" ref="O2:O10" si="2">(LN(G2)-M2)/0.176</f>
         <v>0.11830573385214231</v>
       </c>
-      <c r="W2">
+      <c r="P2">
         <v>4.6420000000000003</v>
       </c>
-      <c r="X2">
+      <c r="Q2">
         <v>3.2309999999999999</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="T2" s="1">
         <f>POWER(2.8,3/2)/POWER(4.35,3/2)</f>
         <v>0.51642012869887588</v>
       </c>
-      <c r="AB2" s="1">
-        <f>1/AA2</f>
+      <c r="U2" s="1">
+        <f>1/T2</f>
         <v>1.9364078672136715</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1">
         <v>30.571428571428573</v>
@@ -1669,91 +1386,76 @@
       <c r="C3" s="2">
         <v>1503</v>
       </c>
-      <c r="D3" s="1">
-        <v>37.531506849315072</v>
-      </c>
-      <c r="G3" s="1">
-        <v>40</v>
-      </c>
-      <c r="H3" s="2">
-        <v>2910</v>
-      </c>
-      <c r="I3" s="2">
-        <v>10</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="D3">
         <f>-1.39 + 0.189*B3</f>
         <v>4.3880000000000008</v>
       </c>
-      <c r="L3" s="4">
+      <c r="E3" s="4">
         <f>(-0.1655 + 0.121125*B3)/(0.0028*B3 + 0.798)</f>
         <v>4.003467955765375</v>
       </c>
-      <c r="M3">
+      <c r="F3">
         <v>2.6</v>
       </c>
-      <c r="N3">
+      <c r="G3">
         <v>4.5</v>
       </c>
-      <c r="O3" s="1">
+      <c r="H3" s="1">
         <f t="shared" si="0"/>
         <v>0.59252506836827701</v>
       </c>
-      <c r="P3" s="1">
+      <c r="I3" s="1">
         <f t="shared" si="0"/>
         <v>1.1240254823370253</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="J3" s="1">
         <f xml:space="preserve"> 2.63/3.84</f>
         <v>0.68489583333333337</v>
       </c>
-      <c r="R3" s="4">
-        <f t="shared" ref="R3:R10" si="3">1/Q3</f>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:K10" si="3">1/J3</f>
         <v>1.4600760456273763</v>
       </c>
-      <c r="S3" s="4">
+      <c r="L3" s="4">
         <f>1.224*LN(B3)-2.822</f>
         <v>1.3641606199430427</v>
       </c>
-      <c r="T3" s="4">
+      <c r="M3" s="4">
         <f>1.396*LN(B3)-3.359</f>
         <v>1.4154119488892869</v>
       </c>
-      <c r="U3" s="4">
+      <c r="N3" s="4">
         <f t="shared" si="1"/>
         <v>-2.4917632616805268</v>
       </c>
-      <c r="V3" s="4">
+      <c r="O3" s="4">
         <f t="shared" si="2"/>
         <v>0.50378095390333677</v>
       </c>
-      <c r="W3">
+      <c r="P3">
         <v>3.1190000000000002</v>
       </c>
-      <c r="X3">
+      <c r="Q3">
         <v>2.5609999999999999</v>
       </c>
-      <c r="Y3">
+      <c r="R3">
         <v>1.8640000000000001</v>
       </c>
-      <c r="Z3">
+      <c r="S3">
         <v>1.3959999999999999</v>
       </c>
-      <c r="AA3" s="1">
+      <c r="T3" s="1">
         <f>POWER(2.63,3/2)/POWER(3.84,3/2)</f>
         <v>0.56680906351658378</v>
       </c>
-      <c r="AB3" s="1">
-        <f t="shared" ref="AB3:AB10" si="4">1/AA3</f>
+      <c r="U3" s="1">
+        <f t="shared" ref="U3:U10" si="4">1/T3</f>
         <v>1.7642625433612917</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1">
         <v>28</v>
@@ -1761,88 +1463,73 @@
       <c r="C4" s="2">
         <v>1224</v>
       </c>
-      <c r="D4" s="1">
-        <v>37.12054794520548</v>
-      </c>
-      <c r="G4" s="1">
-        <v>38</v>
-      </c>
-      <c r="H4" s="2">
-        <v>4060</v>
-      </c>
-      <c r="I4" s="2">
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
+      <c r="D4">
         <f>-1.39 + 0.189*B4</f>
         <v>3.9020000000000001</v>
       </c>
-      <c r="L4" s="4">
+      <c r="E4" s="4">
         <f>(-0.1655 + 0.121125*B4)/(0.0028*B4 + 0.798)</f>
         <v>3.6809675947056131</v>
       </c>
-      <c r="M4">
+      <c r="F4">
         <v>3.1</v>
       </c>
-      <c r="N4">
+      <c r="G4">
         <v>3.9</v>
       </c>
-      <c r="O4" s="1">
+      <c r="H4" s="1">
         <f t="shared" si="0"/>
         <v>0.79446437724243979</v>
       </c>
-      <c r="P4" s="1">
+      <c r="I4" s="1">
         <f t="shared" si="0"/>
         <v>1.0595040297582148</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="J4" s="1">
         <f xml:space="preserve"> 1.79/2.84</f>
         <v>0.63028169014084512</v>
       </c>
-      <c r="R4" s="4">
+      <c r="K4" s="4">
         <f t="shared" si="3"/>
         <v>1.5865921787709496</v>
       </c>
-      <c r="S4" s="4">
+      <c r="L4" s="4">
         <f>1.224*LN(B4)-2.822</f>
         <v>1.2566183204544492</v>
       </c>
-      <c r="T4" s="4">
+      <c r="M4" s="4">
         <f>1.396*LN(B4)-3.359</f>
         <v>1.292757496204584</v>
       </c>
-      <c r="U4" s="4">
+      <c r="N4" s="4">
         <f t="shared" si="1"/>
         <v>-0.76351346928871111</v>
       </c>
-      <c r="V4" s="4">
+      <c r="O4" s="4">
         <f t="shared" si="2"/>
         <v>0.38760827801713976</v>
       </c>
-      <c r="W4">
+      <c r="P4">
         <v>3.3540000000000001</v>
       </c>
-      <c r="X4">
+      <c r="Q4">
         <v>2.48</v>
       </c>
-      <c r="Z4">
+      <c r="S4">
         <v>2.8260000000000001</v>
       </c>
-      <c r="AA4" s="1">
+      <c r="T4" s="1">
         <f xml:space="preserve"> POWER(1.79,3/2)/POWER(2.84,3/2)</f>
         <v>0.50038241220420621</v>
       </c>
-      <c r="AB4" s="1">
+      <c r="U4" s="1">
         <f t="shared" si="4"/>
         <v>1.9984715202018326</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1">
         <v>36.714285714285715</v>
@@ -1850,85 +1537,64 @@
       <c r="C5" s="2">
         <v>2891</v>
       </c>
-      <c r="D5" s="1">
-        <v>41.838356164383562</v>
-      </c>
-      <c r="E5" s="1">
-        <v>63</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="G5" s="1">
-        <v>38.571428571428569</v>
-      </c>
-      <c r="H5" s="2">
-        <v>3480</v>
-      </c>
-      <c r="I5" s="2">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="D5">
         <f>-1.39 + 0.189*B5</f>
         <v>5.5490000000000004</v>
       </c>
-      <c r="L5" s="4">
+      <c r="E5" s="4">
         <f>(-0.1655 + 0.121125*B5)/(0.0028*B5 + 0.798)</f>
         <v>4.753017159350418</v>
       </c>
-      <c r="M5">
+      <c r="F5">
         <v>4.7</v>
       </c>
-      <c r="N5">
+      <c r="G5">
         <v>5</v>
       </c>
-      <c r="O5" s="1">
+      <c r="H5" s="1">
         <f t="shared" si="0"/>
         <v>0.84699945936204724</v>
       </c>
-      <c r="P5" s="1">
+      <c r="I5" s="1">
         <f t="shared" si="0"/>
         <v>1.051963380810377</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="J5" s="1">
         <f xml:space="preserve"> 3.54/4.78</f>
         <v>0.7405857740585774</v>
       </c>
-      <c r="R5" s="4">
+      <c r="K5" s="4">
         <f t="shared" si="3"/>
         <v>1.3502824858757063</v>
       </c>
-      <c r="S5" s="4">
+      <c r="L5" s="4">
         <f>1.224*LN(B5)-2.822</f>
         <v>1.5882751054680453</v>
       </c>
-      <c r="T5" s="4">
+      <c r="M5" s="4">
         <f>1.396*LN(B5)-3.359</f>
         <v>1.6710196464325096</v>
       </c>
-      <c r="U5" s="4">
+      <c r="N5" s="4">
         <f t="shared" si="1"/>
         <v>-0.24824754117092873</v>
       </c>
-      <c r="V5" s="4">
+      <c r="O5" s="4">
         <f t="shared" si="2"/>
         <v>-0.34989621590005271</v>
       </c>
-      <c r="AA5" s="1">
+      <c r="T5" s="1">
         <f xml:space="preserve"> POWER(3.54,3/2)/POWER(4.78,3/2)</f>
         <v>0.63732807216989762</v>
       </c>
-      <c r="AB5" s="1">
+      <c r="U5" s="1">
         <f t="shared" si="4"/>
         <v>1.5690506093593537</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
         <v>27.285714285714285</v>
@@ -1936,91 +1602,70 @@
       <c r="C6" s="2">
         <v>953</v>
       </c>
-      <c r="D6" s="1">
-        <v>38.402739726027399</v>
-      </c>
-      <c r="E6" s="1">
-        <v>55</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="G6" s="1">
-        <v>33</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1700</v>
-      </c>
-      <c r="I6" s="2">
-        <v>8</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="D6">
         <f>-1.39 + 0.189*B6</f>
         <v>3.7670000000000003</v>
       </c>
-      <c r="L6" s="4">
+      <c r="E6" s="4">
         <f>(-0.1655 + 0.121125*B6)/(0.0028*B6 + 0.798)</f>
         <v>3.5904416089400066</v>
       </c>
-      <c r="M6">
+      <c r="F6">
         <v>2.4</v>
       </c>
-      <c r="N6">
+      <c r="G6">
         <v>3.8</v>
       </c>
-      <c r="O6" s="1">
+      <c r="H6" s="1">
         <f t="shared" si="0"/>
         <v>0.63711176002123693</v>
       </c>
-      <c r="P6" s="1">
+      <c r="I6" s="1">
         <f t="shared" si="0"/>
         <v>1.058365631274494</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="J6" s="1">
         <f>1.43/2.15</f>
         <v>0.66511627906976745</v>
       </c>
-      <c r="R6" s="4">
+      <c r="K6" s="4">
         <f t="shared" si="3"/>
         <v>1.5034965034965035</v>
       </c>
-      <c r="S6" s="4">
+      <c r="L6" s="4">
         <f>1.224*LN(B6)-2.822</f>
         <v>1.2249886534853713</v>
       </c>
-      <c r="T6" s="4">
+      <c r="M6" s="4">
         <f>1.396*LN(B6)-3.359</f>
         <v>1.2566831374718772</v>
       </c>
-      <c r="U6" s="4">
+      <c r="N6" s="4">
         <f t="shared" si="1"/>
         <v>-2.1312190008016554</v>
       </c>
-      <c r="V6" s="4">
+      <c r="O6" s="4">
         <f t="shared" si="2"/>
         <v>0.44498823443444757</v>
       </c>
-      <c r="Y6">
+      <c r="R6">
         <v>0.98099999999999998</v>
       </c>
-      <c r="Z6">
+      <c r="S6">
         <v>1.897</v>
       </c>
-      <c r="AA6" s="1">
+      <c r="T6" s="1">
         <f xml:space="preserve"> POWER(1.43,3/2)/POWER(2.15,3/2)</f>
         <v>0.54243332909261388</v>
       </c>
-      <c r="AB6" s="1">
+      <c r="U6" s="1">
         <f t="shared" si="4"/>
         <v>1.843544536012945</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
         <v>32.571428571428569</v>
@@ -2028,85 +1673,64 @@
       <c r="C7" s="2">
         <v>2133</v>
       </c>
-      <c r="D7" s="1">
-        <v>41.30684931506849</v>
-      </c>
-      <c r="E7" s="1">
-        <v>65</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="G7" s="1">
-        <v>40</v>
-      </c>
-      <c r="H7" s="2">
-        <v>3080</v>
-      </c>
-      <c r="I7" s="2">
-        <v>10</v>
-      </c>
-      <c r="J7" s="2">
-        <v>2</v>
-      </c>
-      <c r="K7">
+      <c r="D7">
         <f>-1.39 + 0.189*B7</f>
         <v>4.766</v>
       </c>
-      <c r="L7" s="4">
+      <c r="E7" s="4">
         <f>(-0.1655 + 0.121125*B7)/(0.0028*B7 + 0.798)</f>
         <v>4.2506908296381978</v>
       </c>
-      <c r="M7">
+      <c r="F7">
         <v>3.5</v>
       </c>
-      <c r="N7">
+      <c r="G7">
         <v>4.4000000000000004</v>
       </c>
-      <c r="O7" s="1">
+      <c r="H7" s="1">
         <f t="shared" si="0"/>
         <v>0.7343684431389006</v>
       </c>
-      <c r="P7" s="1">
+      <c r="I7" s="1">
         <f t="shared" si="0"/>
         <v>1.0351258598533526</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="J7" s="1">
         <f>2.02/3.31</f>
         <v>0.61027190332326287</v>
       </c>
-      <c r="R7" s="4">
+      <c r="K7" s="4">
         <f t="shared" si="3"/>
         <v>1.6386138613861385</v>
       </c>
-      <c r="S7" s="4">
+      <c r="L7" s="4">
         <f>1.224*LN(B7)-2.822</f>
         <v>1.4417250273965321</v>
       </c>
-      <c r="T7" s="4">
+      <c r="M7" s="4">
         <f>1.396*LN(B7)-3.359</f>
         <v>1.5038759299391815</v>
       </c>
-      <c r="U7" s="4">
+      <c r="N7" s="4">
         <f t="shared" si="1"/>
         <v>-1.1522076762266098</v>
       </c>
-      <c r="V7" s="4">
+      <c r="O7" s="4">
         <f t="shared" si="2"/>
         <v>-0.12654198303957925</v>
       </c>
-      <c r="AA7" s="1">
+      <c r="T7" s="1">
         <f xml:space="preserve"> POWER(2.02,3/2)/POWER(3.31,3/2)</f>
         <v>0.47674381065133298</v>
       </c>
-      <c r="AB7" s="1">
+      <c r="U7" s="1">
         <f t="shared" si="4"/>
         <v>2.0975626272605159</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1">
         <v>39</v>
@@ -2114,91 +1738,76 @@
       <c r="C8" s="2">
         <v>3047</v>
       </c>
-      <c r="D8" s="1">
-        <v>21.043835616438358</v>
-      </c>
-      <c r="G8" s="1">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2">
-        <v>3140</v>
-      </c>
-      <c r="I8" s="2">
-        <v>9</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="D8">
         <f>-1.39 + 0.189*B8</f>
         <v>5.9810000000000008</v>
       </c>
-      <c r="L8" s="4">
+      <c r="E8" s="4">
         <f>(-0.1655 + 0.121125*B8)/(0.0028*B8 + 0.798)</f>
         <v>5.0246638007054676</v>
       </c>
-      <c r="M8">
+      <c r="F8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="N8">
+      <c r="G8">
         <v>5.6</v>
       </c>
-      <c r="O8" s="1">
+      <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>0.38455107841498071</v>
       </c>
-      <c r="P8" s="1">
+      <c r="I8" s="1">
         <f t="shared" si="0"/>
         <v>1.1145024268516739</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="J8" s="1">
         <f>1.94/4.44</f>
         <v>0.43693693693693686</v>
       </c>
-      <c r="R8" s="4">
+      <c r="K8" s="4">
         <f t="shared" si="3"/>
         <v>2.2886597938144333</v>
       </c>
-      <c r="S8" s="4">
+      <c r="L8" s="4">
         <f>1.224*LN(B8)-2.822</f>
         <v>1.6621994548626873</v>
       </c>
-      <c r="T8" s="4">
+      <c r="M8" s="4">
         <f>1.396*LN(B8)-3.359</f>
         <v>1.755332057996986</v>
       </c>
-      <c r="U8" s="4">
+      <c r="N8" s="4">
         <f t="shared" si="1"/>
         <v>-5.0566483654120935</v>
       </c>
-      <c r="V8" s="4">
+      <c r="O8" s="4">
         <f t="shared" si="2"/>
         <v>-0.18503102418115042</v>
       </c>
-      <c r="W8">
+      <c r="P8">
         <v>4.21</v>
       </c>
-      <c r="X8">
+      <c r="Q8">
         <v>3.0350000000000001</v>
       </c>
-      <c r="Y8">
+      <c r="R8">
         <v>0.85299999999999998</v>
       </c>
-      <c r="Z8">
+      <c r="S8">
         <v>1.4510000000000001</v>
       </c>
-      <c r="AA8" s="1">
+      <c r="T8" s="1">
         <f xml:space="preserve"> POWER(1.94,3/2)/POWER(4.44,3/2)</f>
         <v>0.28882058261706389</v>
       </c>
-      <c r="AB8" s="1">
+      <c r="U8" s="1">
         <f t="shared" si="4"/>
         <v>3.4623571178300043</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1">
         <v>30</v>
@@ -2206,91 +1815,76 @@
       <c r="C9" s="2">
         <v>1608</v>
       </c>
-      <c r="D9" s="1">
-        <v>30.975342465753425</v>
-      </c>
-      <c r="G9" s="1">
-        <v>40.714285714285715</v>
-      </c>
-      <c r="H9" s="2">
-        <v>2970</v>
-      </c>
-      <c r="I9" s="2">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="D9">
         <f>-1.39 + 0.189*B9</f>
         <v>4.28</v>
       </c>
-      <c r="L9" s="4">
+      <c r="E9" s="4">
         <f>(-0.1655 + 0.121125*B9)/(0.0028*B9 + 0.798)</f>
         <v>3.9322562358276643</v>
       </c>
-      <c r="M9">
+      <c r="F9">
         <v>3</v>
       </c>
-      <c r="N9">
+      <c r="G9">
         <v>4.2</v>
       </c>
-      <c r="O9" s="1">
+      <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>0.7009345794392523</v>
       </c>
-      <c r="P9" s="1">
+      <c r="I9" s="1">
         <f t="shared" si="0"/>
         <v>1.0680890939234484</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="J9" s="1">
         <f>1.96/2.32</f>
         <v>0.84482758620689657</v>
       </c>
-      <c r="R9" s="4">
+      <c r="K9" s="4">
         <f t="shared" si="3"/>
         <v>1.1836734693877551</v>
       </c>
-      <c r="S9" s="4">
+      <c r="L9" s="4">
         <f>1.224*LN(B9)-2.822</f>
         <v>1.3410655951544781</v>
       </c>
-      <c r="T9" s="4">
+      <c r="M9" s="4">
         <f>1.396*LN(B9)-3.359</f>
         <v>1.3890715448003688</v>
       </c>
-      <c r="U9" s="4">
+      <c r="N9" s="4">
         <f t="shared" si="1"/>
         <v>-1.4783738200388312</v>
       </c>
-      <c r="V9" s="4">
+      <c r="O9" s="4">
         <f t="shared" si="2"/>
         <v>0.26143738914178394</v>
       </c>
-      <c r="W9">
+      <c r="P9">
         <v>4.1260000000000003</v>
       </c>
-      <c r="X9">
+      <c r="Q9">
         <v>2.8679999999999999</v>
       </c>
-      <c r="Y9">
+      <c r="R9">
         <v>1.0720000000000001</v>
       </c>
-      <c r="Z9">
+      <c r="S9">
         <v>1.9550000000000001</v>
       </c>
-      <c r="AA9" s="1">
+      <c r="T9" s="1">
         <f xml:space="preserve"> POWER(1.96,3/2)/POWER(2.32,3/2)</f>
         <v>0.7765190770842213</v>
       </c>
-      <c r="AB9" s="1">
+      <c r="U9" s="1">
         <f t="shared" si="4"/>
         <v>1.287798367755413</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1">
         <v>28.142857142857142</v>
@@ -2298,87 +1892,72 @@
       <c r="C10" s="2">
         <v>1248</v>
       </c>
-      <c r="D10" s="1">
-        <v>27.936986301369863</v>
-      </c>
-      <c r="G10" s="1">
-        <v>39.714285714285715</v>
-      </c>
-      <c r="H10" s="7">
-        <v>3520</v>
-      </c>
-      <c r="I10">
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="D10">
         <f>-1.39 + 0.189*B10</f>
         <v>3.9290000000000003</v>
       </c>
-      <c r="L10" s="4">
+      <c r="E10" s="4">
         <f>(-0.1655 + 0.121125*B10)/(0.0028*B10 + 0.798)</f>
         <v>3.6990232338373303</v>
       </c>
-      <c r="M10">
+      <c r="F10">
         <v>2</v>
       </c>
-      <c r="N10">
+      <c r="G10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O10" s="1">
+      <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>0.50903537795876808</v>
       </c>
-      <c r="P10" s="1">
+      <c r="I10" s="1">
         <f t="shared" si="0"/>
         <v>1.1084007157604956</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="J10" s="1">
         <f>0.95/2.01</f>
         <v>0.47263681592039802</v>
       </c>
-      <c r="R10" s="4">
+      <c r="K10" s="4">
         <f t="shared" si="3"/>
         <v>2.1157894736842104</v>
       </c>
-      <c r="S10" s="4">
+      <c r="L10" s="4">
         <f>1.224*LN(B10)-2.822</f>
         <v>1.2628473415315939</v>
       </c>
-      <c r="T10" s="4">
+      <c r="M10" s="4">
         <f>1.396*LN(B10)-3.359</f>
         <v>1.2998618372370139</v>
       </c>
-      <c r="U10" s="4">
+      <c r="N10" s="4">
         <f t="shared" si="1"/>
         <v>-3.473781469339321</v>
       </c>
-      <c r="V10" s="4">
+      <c r="O10" s="4">
         <f t="shared" si="2"/>
         <v>0.63139282087072834</v>
       </c>
-      <c r="W10">
+      <c r="P10">
         <v>3.6280000000000001</v>
       </c>
-      <c r="X10">
+      <c r="Q10">
         <v>2.8460000000000001</v>
       </c>
-      <c r="AA10" s="1">
+      <c r="T10" s="1">
         <f xml:space="preserve"> POWER(0.95,3/2)/POWER(2.01,3/2)</f>
         <v>0.3249311306864211</v>
       </c>
-      <c r="AB10" s="1">
+      <c r="U10" s="1">
         <f t="shared" si="4"/>
         <v>3.0775752322884156</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2390,89 +1969,72 @@
         <f>AVERAGE(C10,C9,C8,C7,C6,C5,C4,C3,C2)</f>
         <v>1946.6666666666667</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1">
+        <f t="shared" ref="D12:K12" si="5">AVERAGE(D10,D9,D8,D7,D6,D5,D4,D3,D2)</f>
+        <v>4.6759999999999993</v>
+      </c>
       <c r="E12" s="1">
-        <f>AVERAGE(E10,E9,E8,E7,E6,E5,E4,E3,E2)</f>
-        <v>61.75</v>
-      </c>
-      <c r="F12" s="1">
-        <f>AVERAGE(F10,F9,F8,F7,F6,F5,F4,F3,F2)</f>
-        <v>1.6724999999999999</v>
-      </c>
-      <c r="G12" s="1">
-        <f>MEDIAN(G2:G10)</f>
-        <v>40</v>
-      </c>
-      <c r="H12" s="1">
-        <f>AVERAGE(H10,H9,H8,H7,H6,H5,H4,H3,H2)</f>
-        <v>3187.7777777777778</v>
-      </c>
-      <c r="K12" s="1">
-        <f t="shared" ref="K12:R12" si="5">AVERAGE(K10,K9,K8,K7,K6,K5,K4,K3,K2)</f>
-        <v>4.6759999999999993</v>
-      </c>
-      <c r="L12" s="1">
         <f t="shared" si="5"/>
         <v>4.1856043824935654</v>
       </c>
-      <c r="M12" s="1">
+      <c r="F12" s="1">
         <f t="shared" si="5"/>
         <v>3.0000000000000004</v>
       </c>
-      <c r="N12" s="1">
+      <c r="G12" s="1">
         <f t="shared" si="5"/>
         <v>4.5444444444444443</v>
       </c>
-      <c r="O12" s="1">
+      <c r="H12" s="1">
         <f t="shared" si="5"/>
         <v>0.64618989848423036</v>
       </c>
-      <c r="P12" s="1">
+      <c r="I12" s="1">
         <f t="shared" si="5"/>
         <v>1.0844667494362525</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="J12" s="1">
         <f t="shared" si="5"/>
         <v>0.63658121998995087</v>
       </c>
-      <c r="R12" s="1">
+      <c r="K12" s="1">
         <f t="shared" si="5"/>
         <v>1.6311950267349447</v>
       </c>
+      <c r="N12" s="1">
+        <f>AVERAGE(N2:N10)</f>
+        <v>-2.1099129356547346</v>
+      </c>
+      <c r="O12" s="1">
+        <f>AVERAGE(O2:O10)</f>
+        <v>0.18733824301097737</v>
+      </c>
+      <c r="P12" s="1">
+        <f t="shared" ref="P12:S12" si="6">AVERAGE(P2:P10)</f>
+        <v>3.8465000000000007</v>
+      </c>
+      <c r="Q12" s="1">
+        <f t="shared" si="6"/>
+        <v>2.8368333333333333</v>
+      </c>
+      <c r="R12" s="1">
+        <f t="shared" si="6"/>
+        <v>1.1925000000000001</v>
+      </c>
+      <c r="S12" s="1">
+        <f t="shared" si="6"/>
+        <v>1.905</v>
+      </c>
+      <c r="T12" s="1">
+        <f>AVERAGE(T2:T10)</f>
+        <v>0.51448751185791297</v>
+      </c>
       <c r="U12" s="1">
         <f>AVERAGE(U2:U10)</f>
-        <v>-2.1099129356547346</v>
-      </c>
-      <c r="V12" s="1">
-        <f>AVERAGE(V2:V10)</f>
-        <v>0.18733824301097737</v>
-      </c>
-      <c r="W12" s="1">
-        <f t="shared" ref="W12:Z12" si="6">AVERAGE(W2:W10)</f>
-        <v>3.8465000000000007</v>
-      </c>
-      <c r="X12" s="1">
-        <f t="shared" si="6"/>
-        <v>2.8368333333333333</v>
-      </c>
-      <c r="Y12" s="1">
-        <f t="shared" si="6"/>
-        <v>1.1925000000000001</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" si="6"/>
-        <v>1.905</v>
-      </c>
-      <c r="AA12" s="1">
-        <f>AVERAGE(AA2:AA10)</f>
-        <v>0.51448751185791297</v>
-      </c>
-      <c r="AB12" s="1">
-        <f>AVERAGE(AB2:AB10)</f>
         <v>2.1152256023648266</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2484,98 +2046,76 @@
         <f>STDEV(C10,C9,C8,C7,C6,C5,C4,C3,C2)</f>
         <v>820.08459929448748</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1">
+        <f t="shared" ref="D13:K13" si="7">STDEV(D10,D9,D8,D7,D6,D5,D4,D3,D2)</f>
+        <v>0.8225034954333057</v>
+      </c>
       <c r="E13" s="1">
-        <f>STDEV(E10,E9,E8,E7,E6,E5,E4,E3,E2)</f>
-        <v>4.5734742446707477</v>
-      </c>
-      <c r="F13" s="1">
-        <f>STDEV(F10,F9,F8,F7,F6,F5,F4,F3,F2)</f>
-        <v>6.3442887702247569E-2</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1">
-        <f>STDEV(H10,H9,H8,H7,H6,H5,H4,H3,H2)</f>
-        <v>681.99666014170771</v>
-      </c>
-      <c r="K13" s="1">
-        <f t="shared" ref="K13:R13" si="7">STDEV(K10,K9,K8,K7,K6,K5,K4,K3,K2)</f>
-        <v>0.8225034954333057</v>
-      </c>
-      <c r="L13" s="1">
         <f t="shared" si="7"/>
         <v>0.5333911324907904</v>
       </c>
-      <c r="M13" s="1">
+      <c r="F13" s="1">
         <f t="shared" si="7"/>
         <v>0.8154753215150029</v>
       </c>
-      <c r="N13" s="1">
+      <c r="G13" s="1">
         <f t="shared" si="7"/>
         <v>0.64828834462589013</v>
       </c>
-      <c r="O13" s="1">
+      <c r="H13" s="1">
         <f t="shared" si="7"/>
         <v>0.14328262152225268</v>
       </c>
-      <c r="P13" s="1">
+      <c r="I13" s="1">
         <f t="shared" si="7"/>
         <v>3.7437248444193376E-2</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="J13" s="1">
         <f t="shared" si="7"/>
         <v>0.12492492042253006</v>
       </c>
-      <c r="R13" s="1">
+      <c r="K13" s="1">
         <f t="shared" si="7"/>
         <v>0.35354235823764896</v>
       </c>
+      <c r="N13" s="1">
+        <f>STDEV(N2:N10)</f>
+        <v>1.4701726806808169</v>
+      </c>
+      <c r="O13" s="1">
+        <f>STDEV(O2:O10)</f>
+        <v>0.34275880084821458</v>
+      </c>
+      <c r="P13" s="1">
+        <f t="shared" ref="P13:S13" si="8">STDEV(P2:P10)</f>
+        <v>0.5766502406138353</v>
+      </c>
+      <c r="Q13" s="1">
+        <f t="shared" si="8"/>
+        <v>0.28252675389539073</v>
+      </c>
+      <c r="R13" s="1">
+        <f t="shared" si="8"/>
+        <v>0.45659062627259406</v>
+      </c>
+      <c r="S13" s="1">
+        <f t="shared" si="8"/>
+        <v>0.57358565184286148</v>
+      </c>
+      <c r="T13" s="1">
+        <f>STDEV(T2:T10)</f>
+        <v>0.14821998782312124</v>
+      </c>
       <c r="U13" s="1">
         <f>STDEV(U2:U10)</f>
-        <v>1.4701726806808169</v>
-      </c>
-      <c r="V13" s="1">
-        <f>STDEV(V2:V10)</f>
-        <v>0.34275880084821458</v>
-      </c>
-      <c r="W13" s="1">
-        <f t="shared" ref="W13:Z13" si="8">STDEV(W2:W10)</f>
-        <v>0.5766502406138353</v>
-      </c>
-      <c r="X13" s="1">
-        <f t="shared" si="8"/>
-        <v>0.28252675389539073</v>
-      </c>
-      <c r="Y13" s="1">
-        <f t="shared" si="8"/>
-        <v>0.45659062627259406</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" si="8"/>
-        <v>0.57358565184286148</v>
-      </c>
-      <c r="AA13" s="1">
-        <f>STDEV(AA2:AA10)</f>
-        <v>0.14821998782312124</v>
-      </c>
-      <c r="AB13" s="1">
-        <f>STDEV(AB2:AB10)</f>
         <v>0.70415978576656846</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="G14" s="5">
-        <f>QUARTILE(G2:G10,1)</f>
-        <v>38.571428571428569</v>
-      </c>
-      <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="G15" s="5">
-        <f>QUARTILE(G2:G10,3)</f>
-        <v>40</v>
-      </c>
-      <c r="W15" s="2"/>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
